--- a/ddeprofit.xlsx
+++ b/ddeprofit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E27688-0B5D-4178-B4CE-309E42FFC8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E569AB47-5AE8-44BE-8FDC-FD752713BD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dde profit" sheetId="12" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="superficie_de_volatilidade_de_dolar" localSheetId="1">base_b3!$A$1:$L$51</definedName>
+    <definedName name="superficie_de_volatilidade_de_dolar" localSheetId="1">base_b3!$A$1:$L$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>Ir conteúdo Ir menu Ir rodapé</t>
   </si>
@@ -169,28 +169,25 @@
     <t>FRP0</t>
   </si>
   <si>
-    <t xml:space="preserve">Ícone     </t>
-  </si>
-  <si>
     <t>DOLINDEX</t>
   </si>
   <si>
     <t>GLDFUT</t>
   </si>
   <si>
-    <t xml:space="preserve">   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                                                                                                                                                                           Download do arquivo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Atualizado em: 03/10/2025 </t>
-  </si>
-  <si>
-    <t>Delta%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  * A superfície de volatilidade de dólar é construída com base nas informações coletadas por um pool de Informantes às 18h</t>
+    <t>Delta %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         Atualizado em: 13/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * A superfície de volatilidade de dólar é construída com base nas informações coletadas por um pool de Informantes às 18h</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ícone        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                               Download do arquivo</t>
   </si>
 </sst>
 </file>
@@ -300,112 +297,112 @@
       <ddeItem name="DI1FUT.ABE" advise="1">
         <values>
           <value>
-            <val>13.5</val>
+            <val>13.455</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.FEC" advise="1">
         <values>
           <value>
-            <val>13.465000000000002</val>
+            <val>13.525</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.MAX" advise="1">
         <values>
           <value>
-            <val>13.57</val>
+            <val>13.994999999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.MIN" advise="1">
         <values>
           <value>
-            <val>13.49</val>
+            <val>13.37</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.NEG" advise="1">
         <values>
           <value>
-            <val>41347</val>
+            <val>117314</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.ULT" advise="1">
         <values>
           <value>
-            <val>13.51</val>
+            <val>13.93</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.VAR" advise="1">
         <values>
           <value>
-            <val>0.33419977720015481</val>
+            <val>2.9944547134935391</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.VEN" advise="1">
         <values>
           <value t="str">
-            <val>03/01/2028</val>
+            <val>02/01/2029</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.VOL" advise="1">
         <values>
           <value>
-            <val>32194605757.099998</val>
+            <val>95560612851.149994</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.ABE" advise="1">
         <values>
           <value>
-            <val>97.745896000000002</val>
+            <val>100.306754</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.FEC" advise="1">
         <values>
           <value>
-            <val>97.745896000000002</val>
+            <val>100.304771</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MAX" advise="1">
         <values>
           <value>
-            <val>98.064409999999995</val>
+            <val>100.331935</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MIN" advise="1">
         <values>
           <value>
-            <val>97.641043999999994</val>
+            <val>100.27269699999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.NEG" advise="1">
         <values>
           <value>
-            <val>3856</val>
+            <val>1689</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.ULT" advise="1">
         <values>
           <value>
-            <val>97.992780999999994</val>
+            <val>100.331935</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.VAR" advise="1">
         <values>
           <value>
-            <val>0.25257837935211569</val>
+            <val>2.7081463552718787E-2</val>
           </value>
         </values>
       </ddeItem>
@@ -419,133 +416,133 @@
       <ddeItem name="DOLINDEX.VOL" advise="1">
         <values>
           <value>
-            <val>377327.496224</val>
+            <val>169426.927474</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.ABE" advise="1">
         <values>
           <value>
-            <val>37</val>
+            <val>22.2</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.FEC" advise="1">
         <values>
           <value>
-            <val>39.6</val>
+            <val>23.900000000000002</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.MAX" advise="1">
         <values>
           <value>
-            <val>37.5</val>
+            <val>23.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.MIN" advise="1">
         <values>
           <value>
-            <val>36.9</val>
+            <val>21.9</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.NEG" advise="1">
         <values>
           <value>
-            <val>125</val>
+            <val>114</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.ULT" advise="1">
         <values>
           <value>
-            <val>37.1</val>
+            <val>22.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.VAR" advise="1">
         <values>
           <value>
-            <val>-6.313131313131322</val>
+            <val>-5.8577405857740672</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.VEN" advise="1">
         <values>
           <value t="str">
-            <val>30/10/2025</val>
+            <val>30/03/2026</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.VOL" advise="1">
         <values>
           <value>
-            <val>7036587825</val>
+            <val>4289965750</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.ABE" advise="1">
         <values>
           <value>
-            <val>3889</val>
+            <val>5148.75</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.FEC" advise="1">
         <values>
           <value>
-            <val>3881.5</val>
+            <val>5112.75</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.MAX" advise="1">
         <values>
           <value>
-            <val>3922.75</val>
+            <val>5153</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.MIN" advise="1">
         <values>
           <value>
-            <val>3887.25</val>
+            <val>5046.75</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.NEG" advise="1">
         <values>
           <value>
-            <val>269</val>
+            <val>839</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.ULT" advise="1">
         <values>
           <value>
-            <val>3917</val>
+            <val>5048.25</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.VAR" advise="1">
         <values>
           <value>
-            <val>0.9145948731160729</val>
+            <val>-1.2615520023470737</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.VEN" advise="1">
         <values>
           <value t="str">
-            <val>23/12/2025</val>
+            <val>28/04/2026</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.VOL" advise="1">
         <values>
           <value>
-            <val>6478637.7400000002</val>
+            <val>63473095.75</val>
           </value>
         </values>
       </ddeItem>
@@ -553,49 +550,49 @@
       <ddeItem name="USD/BRL.ABE" advise="1">
         <values>
           <value>
-            <val>5.3368000000000002</val>
+            <val>5.3308999999999997</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.FEC" advise="1">
         <values>
           <value>
-            <val>5.3368000000000002</val>
+            <val>5.3308999999999997</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MAX" advise="1">
         <values>
           <value>
-            <val>5.3384070000000001</val>
+            <val>5.3308999999999997</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MIN" advise="1">
         <values>
           <value>
-            <val>5.3368000000000002</val>
+            <val>5.3308999999999997</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.NEG" advise="1">
         <values>
           <value>
-            <val>3</val>
+            <val>2</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.ULT" advise="1">
         <values>
           <value>
-            <val>5.3384070000000001</val>
+            <val>5.3308999999999997</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.VAR" advise="1">
         <values>
           <value>
-            <val>3.011167740967835E-2</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
@@ -609,63 +606,63 @@
       <ddeItem name="USD/BRL.VOL" advise="1">
         <values>
           <value>
-            <val>16.012007000000001</val>
+            <val>10.661799999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.ABE" advise="1">
         <values>
           <value>
-            <val>5370</val>
+            <val>5262</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.MAX" advise="1">
         <values>
           <value>
-            <val>5399</val>
+            <val>5358.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.MIN" advise="1">
         <values>
           <value>
-            <val>5361.5</val>
+            <val>5237.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.NEG" advise="1">
         <values>
           <value>
-            <val>641795</val>
+            <val>967342</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.ULT" advise="1">
         <values>
           <value>
-            <val>5378</val>
+            <val>5354</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.VAR" advise="1">
         <values>
           <value>
-            <val>-1.8590816136835997E-2</val>
+            <val>1.382313955690222</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.VEN" advise="1">
         <values>
           <value t="str">
-            <val>03/11/2025</val>
+            <val>01/04/2026</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.VOL" advise="1">
         <values>
           <value>
-            <val>142173145050</val>
+            <val>200213358680</val>
           </value>
         </values>
       </ddeItem>
@@ -981,7 +978,7 @@
     <col min="8" max="8" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" customWidth="1"/>
+    <col min="18" max="18" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="10:19" x14ac:dyDescent="0.25">
@@ -1022,39 +1019,39 @@
       </c>
       <c r="K2" cm="1">
         <f t="array" ref="K2">[1]!DI1FUT.ULT</f>
-        <v>13.51</v>
+        <v>13.93</v>
       </c>
       <c r="L2" cm="1">
         <f t="array" ref="L2">[1]!DI1FUT.ABE</f>
-        <v>13.5</v>
+        <v>13.455</v>
       </c>
       <c r="M2" cm="1">
         <f t="array" ref="M2">[1]!DI1FUT.MAX</f>
-        <v>13.57</v>
+        <v>13.994999999999999</v>
       </c>
       <c r="N2" cm="1">
         <f t="array" ref="N2">[1]!DI1FUT.MIN</f>
-        <v>13.49</v>
+        <v>13.37</v>
       </c>
       <c r="O2" cm="1">
         <f t="array" ref="O2">[1]!DI1FUT.FEC</f>
-        <v>13.465000000000002</v>
+        <v>13.525</v>
       </c>
       <c r="P2" cm="1">
         <f t="array" ref="P2">[1]!DI1FUT.VAR</f>
-        <v>0.33419977720015481</v>
+        <v>2.9944547134935391</v>
       </c>
       <c r="Q2" cm="1">
         <f t="array" ref="Q2">[1]!DI1FUT.NEG</f>
-        <v>41347</v>
+        <v>117314</v>
       </c>
       <c r="R2" cm="1">
         <f t="array" ref="R2">[1]!DI1FUT.VOL</f>
-        <v>32194605757.099998</v>
+        <v>95560612851.149994</v>
       </c>
       <c r="S2" t="str" cm="1">
         <f t="array" ref="S2">[1]!DI1FUT.VEN</f>
-        <v>03/01/2028</v>
+        <v>02/01/2029</v>
       </c>
     </row>
     <row r="3" spans="10:19" x14ac:dyDescent="0.25">
@@ -1063,39 +1060,39 @@
       </c>
       <c r="K3" cm="1">
         <f t="array" ref="K3">[1]!FRP0.ULT</f>
-        <v>37.1</v>
+        <v>22.5</v>
       </c>
       <c r="L3" cm="1">
         <f t="array" ref="L3">[1]!FRP0.ABE</f>
-        <v>37</v>
+        <v>22.2</v>
       </c>
       <c r="M3" cm="1">
         <f t="array" ref="M3">[1]!FRP0.MAX</f>
-        <v>37.5</v>
+        <v>23.5</v>
       </c>
       <c r="N3" cm="1">
         <f t="array" ref="N3">[1]!FRP0.MIN</f>
-        <v>36.9</v>
+        <v>21.9</v>
       </c>
       <c r="O3" cm="1">
         <f t="array" ref="O3">[1]!FRP0.FEC</f>
-        <v>39.6</v>
+        <v>23.900000000000002</v>
       </c>
       <c r="P3" cm="1">
         <f t="array" ref="P3">[1]!FRP0.VAR</f>
-        <v>-6.313131313131322</v>
+        <v>-5.8577405857740672</v>
       </c>
       <c r="Q3" cm="1">
         <f t="array" ref="Q3">[1]!FRP0.NEG</f>
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="R3" cm="1">
         <f t="array" ref="R3">[1]!FRP0.VOL</f>
-        <v>7036587825</v>
+        <v>4289965750</v>
       </c>
       <c r="S3" t="str" cm="1">
         <f t="array" ref="S3">[1]!FRP0.VEN</f>
-        <v>30/10/2025</v>
+        <v>30/03/2026</v>
       </c>
     </row>
     <row r="4" spans="10:19" x14ac:dyDescent="0.25">
@@ -1104,35 +1101,35 @@
       </c>
       <c r="K4" cm="1">
         <f t="array" ref="K4">[1]!'USD/BRL.ULT'</f>
-        <v>5.3384070000000001</v>
+        <v>5.3308999999999997</v>
       </c>
       <c r="L4" cm="1">
         <f t="array" ref="L4">[1]!'USD/BRL.ABE'</f>
-        <v>5.3368000000000002</v>
+        <v>5.3308999999999997</v>
       </c>
       <c r="M4" cm="1">
         <f t="array" ref="M4">[1]!'USD/BRL.MAX'</f>
-        <v>5.3384070000000001</v>
+        <v>5.3308999999999997</v>
       </c>
       <c r="N4" cm="1">
         <f t="array" ref="N4">[1]!'USD/BRL.MIN'</f>
-        <v>5.3368000000000002</v>
+        <v>5.3308999999999997</v>
       </c>
       <c r="O4" cm="1">
         <f t="array" ref="O4">[1]!'USD/BRL.FEC'</f>
-        <v>5.3368000000000002</v>
+        <v>5.3308999999999997</v>
       </c>
       <c r="P4" cm="1">
         <f t="array" ref="P4">[1]!'USD/BRL.VAR'</f>
-        <v>3.011167740967835E-2</v>
+        <v>0</v>
       </c>
       <c r="Q4" cm="1">
         <f t="array" ref="Q4">[1]!'USD/BRL.NEG'</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" cm="1">
         <f t="array" ref="R4">[1]!'USD/BRL.VOL'</f>
-        <v>16.012007000000001</v>
+        <v>10.661799999999999</v>
       </c>
       <c r="S4" t="str" cm="1">
         <f t="array" ref="S4">[1]!'USD/BRL.VEN'</f>
@@ -1145,75 +1142,75 @@
       </c>
       <c r="K5" cm="1">
         <f t="array" ref="K5">[1]!WDOFUT.ULT</f>
-        <v>5378</v>
+        <v>5354</v>
       </c>
       <c r="L5" cm="1">
         <f t="array" ref="L5">[1]!WDOFUT.ABE</f>
-        <v>5370</v>
+        <v>5262</v>
       </c>
       <c r="M5" cm="1">
         <f t="array" ref="M5">[1]!WDOFUT.MAX</f>
-        <v>5399</v>
+        <v>5358.5</v>
       </c>
       <c r="N5" cm="1">
         <f t="array" ref="N5">[1]!WDOFUT.MIN</f>
-        <v>5361.5</v>
+        <v>5237.5</v>
       </c>
       <c r="O5">
-        <v>5378</v>
+        <v>5339.5</v>
       </c>
       <c r="P5" cm="1">
         <f t="array" ref="P5">[1]!WDOFUT.VAR</f>
-        <v>-1.8590816136835997E-2</v>
+        <v>1.382313955690222</v>
       </c>
       <c r="Q5" cm="1">
         <f t="array" ref="Q5">[1]!WDOFUT.NEG</f>
-        <v>641795</v>
+        <v>967342</v>
       </c>
       <c r="R5" cm="1">
         <f t="array" ref="R5">[1]!WDOFUT.VOL</f>
-        <v>142173145050</v>
+        <v>200213358680</v>
       </c>
       <c r="S5" t="str" cm="1">
         <f t="array" ref="S5">[1]!WDOFUT.VEN</f>
-        <v>03/11/2025</v>
+        <v>01/04/2026</v>
       </c>
     </row>
     <row r="6" spans="10:19" x14ac:dyDescent="0.25">
       <c r="J6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K6" cm="1">
         <f t="array" ref="K6">[1]!DOLINDEX.ULT</f>
-        <v>97.992780999999994</v>
+        <v>100.331935</v>
       </c>
       <c r="L6" cm="1">
         <f t="array" ref="L6">[1]!DOLINDEX.ABE</f>
-        <v>97.745896000000002</v>
+        <v>100.306754</v>
       </c>
       <c r="M6" cm="1">
         <f t="array" ref="M6">[1]!DOLINDEX.MAX</f>
-        <v>98.064409999999995</v>
+        <v>100.331935</v>
       </c>
       <c r="N6" cm="1">
         <f t="array" ref="N6">[1]!DOLINDEX.MIN</f>
-        <v>97.641043999999994</v>
+        <v>100.27269699999999</v>
       </c>
       <c r="O6" cm="1">
         <f t="array" ref="O6">[1]!DOLINDEX.FEC</f>
-        <v>97.745896000000002</v>
+        <v>100.304771</v>
       </c>
       <c r="P6" cm="1">
         <f t="array" ref="P6">[1]!DOLINDEX.VAR</f>
-        <v>0.25257837935211569</v>
+        <v>2.7081463552718787E-2</v>
       </c>
       <c r="Q6" cm="1">
         <f t="array" ref="Q6">[1]!DOLINDEX.NEG</f>
-        <v>3856</v>
+        <v>1689</v>
       </c>
       <c r="R6" cm="1">
         <f t="array" ref="R6">[1]!DOLINDEX.VOL</f>
-        <v>377327.496224</v>
+        <v>169426.927474</v>
       </c>
       <c r="S6" t="str" cm="1">
         <f t="array" ref="S6">[1]!DOLINDEX.VEN</f>
@@ -1222,43 +1219,43 @@
     </row>
     <row r="7" spans="10:19" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K7" cm="1">
         <f t="array" ref="K7">[1]!GLDFUT.ULT</f>
-        <v>3917</v>
+        <v>5048.25</v>
       </c>
       <c r="L7" cm="1">
         <f t="array" ref="L7">[1]!GLDFUT.ABE</f>
-        <v>3889</v>
+        <v>5148.75</v>
       </c>
       <c r="M7" cm="1">
         <f t="array" ref="M7">[1]!GLDFUT.MAX</f>
-        <v>3922.75</v>
+        <v>5153</v>
       </c>
       <c r="N7" cm="1">
         <f t="array" ref="N7">[1]!GLDFUT.MIN</f>
-        <v>3887.25</v>
+        <v>5046.75</v>
       </c>
       <c r="O7" cm="1">
         <f t="array" ref="O7">[1]!GLDFUT.FEC</f>
-        <v>3881.5</v>
+        <v>5112.75</v>
       </c>
       <c r="P7" cm="1">
         <f t="array" ref="P7">[1]!GLDFUT.VAR</f>
-        <v>0.9145948731160729</v>
+        <v>-1.2615520023470737</v>
       </c>
       <c r="Q7" cm="1">
         <f t="array" ref="Q7">[1]!GLDFUT.NEG</f>
-        <v>269</v>
+        <v>839</v>
       </c>
       <c r="R7" cm="1">
         <f t="array" ref="R7">[1]!GLDFUT.VOL</f>
-        <v>6478637.7400000002</v>
+        <v>63473095.75</v>
       </c>
       <c r="S7" t="str" cm="1">
         <f t="array" ref="S7">[1]!GLDFUT.VEN</f>
-        <v>23/12/2025</v>
+        <v>28/04/2026</v>
       </c>
     </row>
   </sheetData>
@@ -1269,7 +1266,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Planilha10"/>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="5" customWidth="1"/>
@@ -1357,12 +1354,12 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B18" s="4">
         <v>1</v>
@@ -1400,800 +1397,800 @@
     </row>
     <row r="19" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>45962</v>
+        <v>46113</v>
       </c>
       <c r="B19" s="4">
-        <v>17.79</v>
+        <v>20.98</v>
       </c>
       <c r="C19" s="4">
-        <v>16.23</v>
+        <v>20.38</v>
       </c>
       <c r="D19" s="4">
-        <v>14.67</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="E19" s="4">
-        <v>11.95</v>
+        <v>17.02</v>
       </c>
       <c r="F19" s="4">
-        <v>10.79</v>
+        <v>15.67</v>
       </c>
       <c r="G19" s="4">
-        <v>9.9700000000000006</v>
+        <v>14.69</v>
       </c>
       <c r="H19" s="4">
-        <v>9.5500000000000007</v>
+        <v>13.9</v>
       </c>
       <c r="I19" s="4">
-        <v>9.09</v>
+        <v>13.1</v>
       </c>
       <c r="J19" s="4">
-        <v>9.39</v>
+        <v>12.42</v>
       </c>
       <c r="K19" s="4">
-        <v>9.49</v>
+        <v>13.44</v>
       </c>
       <c r="L19" s="4">
-        <v>9.58</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>45992</v>
+        <v>46143</v>
       </c>
       <c r="B20" s="4">
-        <v>16.52</v>
+        <v>21.16</v>
       </c>
       <c r="C20" s="4">
-        <v>16.18</v>
+        <v>20.5</v>
       </c>
       <c r="D20" s="4">
-        <v>15.66</v>
+        <v>19.649999999999999</v>
       </c>
       <c r="E20" s="4">
-        <v>13.17</v>
+        <v>16.95</v>
       </c>
       <c r="F20" s="4">
-        <v>11.66</v>
+        <v>15.55</v>
       </c>
       <c r="G20" s="4">
-        <v>10.82</v>
+        <v>14.5</v>
       </c>
       <c r="H20" s="4">
-        <v>10.18</v>
+        <v>13.71</v>
       </c>
       <c r="I20" s="4">
-        <v>9.83</v>
+        <v>12.88</v>
       </c>
       <c r="J20" s="4">
-        <v>10.24</v>
+        <v>12.21</v>
       </c>
       <c r="K20" s="4">
-        <v>10.15</v>
+        <v>12.06</v>
       </c>
       <c r="L20" s="4">
-        <v>9.99</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>46023</v>
+        <v>46174</v>
       </c>
       <c r="B21" s="4">
-        <v>17.420000000000002</v>
+        <v>20.75</v>
       </c>
       <c r="C21" s="4">
-        <v>16.95</v>
+        <v>19.97</v>
       </c>
       <c r="D21" s="4">
-        <v>16.29</v>
+        <v>19.04</v>
       </c>
       <c r="E21" s="4">
-        <v>13.73</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="F21" s="4">
-        <v>12.15</v>
+        <v>15.28</v>
       </c>
       <c r="G21" s="4">
-        <v>11.29</v>
+        <v>14.34</v>
       </c>
       <c r="H21" s="4">
-        <v>10.63</v>
+        <v>13.65</v>
       </c>
       <c r="I21" s="4">
-        <v>10.34</v>
+        <v>12.91</v>
       </c>
       <c r="J21" s="4">
-        <v>10.81</v>
+        <v>12.38</v>
       </c>
       <c r="K21" s="4">
-        <v>10.8</v>
+        <v>12.25</v>
       </c>
       <c r="L21" s="4">
-        <v>10.78</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>46054</v>
+        <v>46204</v>
       </c>
       <c r="B22" s="4">
-        <v>18.07</v>
+        <v>20.92</v>
       </c>
       <c r="C22" s="4">
-        <v>17.54</v>
+        <v>20.09</v>
       </c>
       <c r="D22" s="4">
-        <v>16.82</v>
+        <v>19.12</v>
       </c>
       <c r="E22" s="4">
-        <v>14.23</v>
+        <v>16.62</v>
       </c>
       <c r="F22" s="4">
-        <v>12.64</v>
+        <v>15.6</v>
       </c>
       <c r="G22" s="4">
-        <v>11.78</v>
+        <v>14.41</v>
       </c>
       <c r="H22" s="4">
-        <v>11.1</v>
+        <v>13.74</v>
       </c>
       <c r="I22" s="4">
-        <v>10.86</v>
+        <v>13.05</v>
       </c>
       <c r="J22" s="4">
-        <v>11.37</v>
+        <v>12.61</v>
       </c>
       <c r="K22" s="4">
-        <v>11.43</v>
+        <v>12.55</v>
       </c>
       <c r="L22" s="4">
-        <v>11.47</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>46082</v>
+        <v>46235</v>
       </c>
       <c r="B23" s="4">
-        <v>18.5</v>
+        <v>20.8</v>
       </c>
       <c r="C23" s="4">
-        <v>17.989999999999998</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D23" s="4">
-        <v>17.3</v>
+        <v>19.05</v>
       </c>
       <c r="E23" s="4">
-        <v>14.72</v>
+        <v>16.66</v>
       </c>
       <c r="F23" s="4">
-        <v>13.15</v>
+        <v>15.64</v>
       </c>
       <c r="G23" s="4">
-        <v>12.29</v>
+        <v>14.5</v>
       </c>
       <c r="H23" s="4">
-        <v>11.63</v>
+        <v>13.87</v>
       </c>
       <c r="I23" s="4">
-        <v>11.39</v>
+        <v>13.21</v>
       </c>
       <c r="J23" s="4">
-        <v>11.92</v>
+        <v>12.83</v>
       </c>
       <c r="K23" s="4">
-        <v>11.96</v>
+        <v>12.79</v>
       </c>
       <c r="L23" s="4">
-        <v>11.98</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>46113</v>
+        <v>46266</v>
       </c>
       <c r="B24" s="4">
-        <v>18.7</v>
+        <v>20.66</v>
       </c>
       <c r="C24" s="4">
-        <v>18.27</v>
+        <v>19.88</v>
       </c>
       <c r="D24" s="4">
-        <v>17.649999999999999</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="E24" s="4">
-        <v>15.07</v>
+        <v>16.690000000000001</v>
       </c>
       <c r="F24" s="4">
-        <v>13.54</v>
+        <v>15.68</v>
       </c>
       <c r="G24" s="4">
-        <v>12.67</v>
+        <v>14.58</v>
       </c>
       <c r="H24" s="4">
-        <v>12.04</v>
+        <v>13.97</v>
       </c>
       <c r="I24" s="4">
-        <v>11.78</v>
+        <v>13.35</v>
       </c>
       <c r="J24" s="4">
-        <v>12.32</v>
+        <v>13.04</v>
       </c>
       <c r="K24" s="4">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="L24" s="4">
-        <v>12.27</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>46143</v>
+        <v>46296</v>
       </c>
       <c r="B25" s="4">
-        <v>19.03</v>
+        <v>20.92</v>
       </c>
       <c r="C25" s="4">
-        <v>18.61</v>
+        <v>20.22</v>
       </c>
       <c r="D25" s="4">
-        <v>18</v>
+        <v>19.38</v>
       </c>
       <c r="E25" s="4">
-        <v>15.24</v>
+        <v>17.03</v>
       </c>
       <c r="F25" s="4">
-        <v>14.14</v>
+        <v>16</v>
       </c>
       <c r="G25" s="4">
-        <v>13.1</v>
+        <v>14.83</v>
       </c>
       <c r="H25" s="4">
-        <v>12.59</v>
+        <v>14.28</v>
       </c>
       <c r="I25" s="4">
-        <v>12.17</v>
+        <v>13.67</v>
       </c>
       <c r="J25" s="4">
-        <v>12.69</v>
+        <v>13.41</v>
       </c>
       <c r="K25" s="4">
-        <v>12.66</v>
+        <v>13.38</v>
       </c>
       <c r="L25" s="4">
-        <v>12.61</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>46174</v>
+        <v>46327</v>
       </c>
       <c r="B26" s="4">
-        <v>18.89</v>
+        <v>21.32</v>
       </c>
       <c r="C26" s="4">
-        <v>18.27</v>
+        <v>20.64</v>
       </c>
       <c r="D26" s="4">
-        <v>17.54</v>
+        <v>19.79</v>
       </c>
       <c r="E26" s="4">
-        <v>15.65</v>
+        <v>17.38</v>
       </c>
       <c r="F26" s="4">
-        <v>14.45</v>
+        <v>16.13</v>
       </c>
       <c r="G26" s="4">
-        <v>13.46</v>
+        <v>15.23</v>
       </c>
       <c r="H26" s="4">
-        <v>12.8</v>
+        <v>14.64</v>
       </c>
       <c r="I26" s="4">
-        <v>12.48</v>
+        <v>14</v>
       </c>
       <c r="J26" s="4">
-        <v>12.47</v>
+        <v>13.73</v>
       </c>
       <c r="K26" s="4">
-        <v>12.54</v>
+        <v>13.77</v>
       </c>
       <c r="L26" s="4">
-        <v>12.67</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>46204</v>
+        <v>46357</v>
       </c>
       <c r="B27" s="4">
-        <v>19.64</v>
+        <v>21.38</v>
       </c>
       <c r="C27" s="4">
-        <v>19.22</v>
+        <v>20.77</v>
       </c>
       <c r="D27" s="4">
-        <v>18.600000000000001</v>
+        <v>20.03</v>
       </c>
       <c r="E27" s="4">
-        <v>15.99</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="F27" s="4">
-        <v>14.67</v>
+        <v>16.690000000000001</v>
       </c>
       <c r="G27" s="4">
-        <v>13.59</v>
+        <v>15.61</v>
       </c>
       <c r="H27" s="4">
-        <v>12.97</v>
+        <v>14.77</v>
       </c>
       <c r="I27" s="4">
-        <v>12.72</v>
+        <v>14.29</v>
       </c>
       <c r="J27" s="4">
-        <v>13.31</v>
+        <v>14.27</v>
       </c>
       <c r="K27" s="4">
-        <v>13.28</v>
+        <v>14.21</v>
       </c>
       <c r="L27" s="4">
-        <v>13.24</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>46235</v>
+        <v>46388</v>
       </c>
       <c r="B28" s="4">
-        <v>20.05</v>
+        <v>21.31</v>
       </c>
       <c r="C28" s="4">
-        <v>19.61</v>
+        <v>20.68</v>
       </c>
       <c r="D28" s="4">
-        <v>18.98</v>
+        <v>19.91</v>
       </c>
       <c r="E28" s="4">
-        <v>16.38</v>
+        <v>17.690000000000001</v>
       </c>
       <c r="F28" s="4">
-        <v>15.05</v>
+        <v>16.739999999999998</v>
       </c>
       <c r="G28" s="4">
-        <v>13.98</v>
+        <v>15.7</v>
       </c>
       <c r="H28" s="4">
-        <v>13.36</v>
+        <v>15.16</v>
       </c>
       <c r="I28" s="4">
-        <v>13.12</v>
+        <v>14.63</v>
       </c>
       <c r="J28" s="4">
-        <v>13.7</v>
+        <v>14.48</v>
       </c>
       <c r="K28" s="4">
-        <v>13.69</v>
+        <v>14.4</v>
       </c>
       <c r="L28" s="4">
-        <v>13.66</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>46266</v>
+        <v>46419</v>
       </c>
       <c r="B29" s="4">
-        <v>19.7</v>
+        <v>21.33</v>
       </c>
       <c r="C29" s="4">
-        <v>19.059999999999999</v>
+        <v>20.65</v>
       </c>
       <c r="D29" s="4">
-        <v>18.309999999999999</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="E29" s="4">
-        <v>16.37</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="F29" s="4">
-        <v>15</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="G29" s="4">
-        <v>14.15</v>
+        <v>15.48</v>
       </c>
       <c r="H29" s="4">
-        <v>13.5</v>
+        <v>14.93</v>
       </c>
       <c r="I29" s="4">
-        <v>13.21</v>
+        <v>14.33</v>
       </c>
       <c r="J29" s="4">
-        <v>13.26</v>
+        <v>14.1</v>
       </c>
       <c r="K29" s="4">
-        <v>13.36</v>
+        <v>14.14</v>
       </c>
       <c r="L29" s="4">
-        <v>13.51</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>46296</v>
+        <v>46447</v>
       </c>
       <c r="B30" s="4">
-        <v>19.82</v>
+        <v>21.23</v>
       </c>
       <c r="C30" s="4">
-        <v>19.190000000000001</v>
+        <v>20.56</v>
       </c>
       <c r="D30" s="4">
-        <v>18.440000000000001</v>
+        <v>19.78</v>
       </c>
       <c r="E30" s="4">
-        <v>16.510000000000002</v>
+        <v>17.82</v>
       </c>
       <c r="F30" s="4">
-        <v>15.29</v>
+        <v>16.36</v>
       </c>
       <c r="G30" s="4">
-        <v>14.31</v>
+        <v>15.51</v>
       </c>
       <c r="H30" s="4">
-        <v>13.67</v>
+        <v>14.98</v>
       </c>
       <c r="I30" s="4">
-        <v>13.38</v>
+        <v>14.39</v>
       </c>
       <c r="J30" s="4">
-        <v>13.44</v>
+        <v>14.19</v>
       </c>
       <c r="K30" s="4">
-        <v>13.55</v>
+        <v>14.23</v>
       </c>
       <c r="L30" s="4">
-        <v>13.7</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>46357</v>
+        <v>46478</v>
       </c>
       <c r="B31" s="4">
-        <v>19.989999999999998</v>
+        <v>20.75</v>
       </c>
       <c r="C31" s="4">
-        <v>19.37</v>
+        <v>20.239999999999998</v>
       </c>
       <c r="D31" s="4">
-        <v>18.649999999999999</v>
+        <v>19.59</v>
       </c>
       <c r="E31" s="4">
-        <v>16.77</v>
+        <v>17.7</v>
       </c>
       <c r="F31" s="4">
-        <v>15.59</v>
+        <v>16.37</v>
       </c>
       <c r="G31" s="4">
-        <v>14.65</v>
+        <v>15.54</v>
       </c>
       <c r="H31" s="4">
-        <v>14.04</v>
+        <v>15.05</v>
       </c>
       <c r="I31" s="4">
-        <v>13.79</v>
+        <v>14.6</v>
       </c>
       <c r="J31" s="4">
-        <v>13.88</v>
+        <v>14.62</v>
       </c>
       <c r="K31" s="4">
-        <v>13.99</v>
+        <v>14.53</v>
       </c>
       <c r="L31" s="4">
-        <v>14.15</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>46388</v>
+        <v>46569</v>
       </c>
       <c r="B32" s="4">
-        <v>20.98</v>
+        <v>21.28</v>
       </c>
       <c r="C32" s="4">
-        <v>20.54</v>
+        <v>20.65</v>
       </c>
       <c r="D32" s="4">
-        <v>19.91</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="E32" s="4">
-        <v>17.27</v>
+        <v>18.12</v>
       </c>
       <c r="F32" s="4">
-        <v>15.94</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="G32" s="4">
-        <v>14.88</v>
+        <v>15.99</v>
       </c>
       <c r="H32" s="4">
-        <v>14.28</v>
+        <v>15.53</v>
       </c>
       <c r="I32" s="4">
-        <v>14.06</v>
+        <v>15.07</v>
       </c>
       <c r="J32" s="4">
-        <v>14.7</v>
+        <v>15.02</v>
       </c>
       <c r="K32" s="4">
-        <v>14.7</v>
+        <v>15.02</v>
       </c>
       <c r="L32" s="4">
-        <v>14.69</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
-        <v>46478</v>
+        <v>46600</v>
       </c>
       <c r="B33" s="4">
-        <v>20.69</v>
+        <v>21.84</v>
       </c>
       <c r="C33" s="4">
-        <v>20.05</v>
+        <v>21.1</v>
       </c>
       <c r="D33" s="4">
-        <v>19.3</v>
+        <v>20.25</v>
       </c>
       <c r="E33" s="4">
-        <v>17.37</v>
+        <v>18.12</v>
       </c>
       <c r="F33" s="4">
-        <v>16.170000000000002</v>
+        <v>16.77</v>
       </c>
       <c r="G33" s="4">
-        <v>15.21</v>
+        <v>15.88</v>
       </c>
       <c r="H33" s="4">
-        <v>14.62</v>
+        <v>15.48</v>
       </c>
       <c r="I33" s="4">
-        <v>14.39</v>
+        <v>15</v>
       </c>
       <c r="J33" s="4">
-        <v>14.53</v>
+        <v>15.3</v>
       </c>
       <c r="K33" s="4">
-        <v>14.67</v>
+        <v>15.53</v>
       </c>
       <c r="L33" s="4">
-        <v>14.85</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>46569</v>
+        <v>46661</v>
       </c>
       <c r="B34" s="4">
-        <v>21.91</v>
+        <v>21.69</v>
       </c>
       <c r="C34" s="4">
-        <v>21.39</v>
+        <v>20.97</v>
       </c>
       <c r="D34" s="4">
-        <v>20.68</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="E34" s="4">
-        <v>17.97</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="F34" s="4">
-        <v>16.579999999999998</v>
+        <v>16.77</v>
       </c>
       <c r="G34" s="4">
-        <v>15.51</v>
+        <v>15.88</v>
       </c>
       <c r="H34" s="4">
-        <v>14.91</v>
+        <v>15.48</v>
       </c>
       <c r="I34" s="4">
-        <v>14.75</v>
+        <v>15.01</v>
       </c>
       <c r="J34" s="4">
-        <v>15.47</v>
+        <v>15.21</v>
       </c>
       <c r="K34" s="4">
-        <v>15.56</v>
+        <v>15.39</v>
       </c>
       <c r="L34" s="4">
-        <v>15.6</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46600</v>
+        <v>46753</v>
       </c>
       <c r="B35" s="1">
-        <v>21.86</v>
+        <v>21.72</v>
       </c>
       <c r="C35" s="1">
-        <v>21.28</v>
+        <v>21.1</v>
       </c>
       <c r="D35" s="1">
-        <v>20.52</v>
+        <v>20.350000000000001</v>
       </c>
       <c r="E35" s="1">
-        <v>18.05</v>
+        <v>18.28</v>
       </c>
       <c r="F35" s="1">
-        <v>16.7</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="G35" s="1">
-        <v>15.66</v>
+        <v>16.37</v>
       </c>
       <c r="H35" s="1">
-        <v>15.06</v>
+        <v>15.89</v>
       </c>
       <c r="I35" s="1">
-        <v>14.88</v>
+        <v>15.37</v>
       </c>
       <c r="J35" s="1">
-        <v>15.41</v>
+        <v>15.19</v>
       </c>
       <c r="K35" s="1">
-        <v>15.55</v>
+        <v>15.23</v>
       </c>
       <c r="L35" s="1">
-        <v>15.65</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46661</v>
+        <v>46844</v>
       </c>
       <c r="B36" s="1">
-        <v>21.79</v>
+        <v>21.94</v>
       </c>
       <c r="C36" s="1">
-        <v>21.1</v>
+        <v>21.27</v>
       </c>
       <c r="D36" s="1">
-        <v>20.29</v>
+        <v>20.440000000000001</v>
       </c>
       <c r="E36" s="1">
-        <v>18.2</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="F36" s="1">
-        <v>16.920000000000002</v>
+        <v>17.03</v>
       </c>
       <c r="G36" s="1">
-        <v>15.91</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="H36" s="1">
-        <v>15.31</v>
+        <v>15.73</v>
       </c>
       <c r="I36" s="1">
-        <v>15.1</v>
+        <v>15.25</v>
       </c>
       <c r="J36" s="1">
-        <v>15.33</v>
+        <v>15.48</v>
       </c>
       <c r="K36" s="1">
-        <v>15.52</v>
+        <v>15.67</v>
       </c>
       <c r="L36" s="1">
-        <v>15.72</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46753</v>
+        <v>46935</v>
       </c>
       <c r="B37" s="1">
-        <v>22.08</v>
+        <v>21.86</v>
       </c>
       <c r="C37" s="1">
-        <v>21.33</v>
+        <v>21.26</v>
       </c>
       <c r="D37" s="1">
-        <v>20.46</v>
+        <v>20.53</v>
       </c>
       <c r="E37" s="1">
-        <v>18.239999999999998</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="F37" s="1">
-        <v>16.88</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="G37" s="1">
-        <v>15.84</v>
+        <v>16.46</v>
       </c>
       <c r="H37" s="1">
-        <v>15.23</v>
+        <v>15.98</v>
       </c>
       <c r="I37" s="1">
-        <v>15.07</v>
+        <v>15.46</v>
       </c>
       <c r="J37" s="1">
-        <v>15.39</v>
+        <v>15.29</v>
       </c>
       <c r="K37" s="1">
-        <v>15.62</v>
+        <v>15.33</v>
       </c>
       <c r="L37" s="1">
-        <v>15.87</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46935</v>
+        <v>47119</v>
       </c>
       <c r="B38" s="1">
-        <v>22.37</v>
+        <v>22.64</v>
       </c>
       <c r="C38" s="1">
-        <v>21.6</v>
+        <v>21.98</v>
       </c>
       <c r="D38" s="1">
-        <v>20.7</v>
+        <v>21.22</v>
       </c>
       <c r="E38" s="1">
-        <v>18.399999999999999</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="F38" s="1">
-        <v>17</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="G38" s="1">
-        <v>15.92</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="H38" s="1">
-        <v>15.29</v>
+        <v>16.57</v>
       </c>
       <c r="I38" s="1">
-        <v>15.11</v>
+        <v>16.02</v>
       </c>
       <c r="J38" s="1">
-        <v>15.44</v>
+        <v>15.79</v>
       </c>
       <c r="K38" s="1">
-        <v>15.67</v>
+        <v>15.82</v>
       </c>
       <c r="L38" s="1">
-        <v>15.92</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>47119</v>
+        <v>47209</v>
       </c>
       <c r="B39" s="1">
-        <v>22.5</v>
+        <v>23.58</v>
       </c>
       <c r="C39" s="1">
-        <v>21.72</v>
+        <v>22.86</v>
       </c>
       <c r="D39" s="1">
-        <v>20.81</v>
+        <v>22.02</v>
       </c>
       <c r="E39" s="1">
-        <v>18.48</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="F39" s="1">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="G39" s="1">
+        <v>17.41</v>
+      </c>
+      <c r="H39" s="1">
+        <v>16.739999999999998</v>
+      </c>
+      <c r="I39" s="1">
+        <v>16.489999999999998</v>
+      </c>
+      <c r="J39" s="1">
+        <v>16.61</v>
+      </c>
+      <c r="K39" s="1">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="L39" s="1">
         <v>16.95</v>
-      </c>
-      <c r="G39" s="1">
-        <v>15.98</v>
-      </c>
-      <c r="H39" s="1">
-        <v>15.35</v>
-      </c>
-      <c r="I39" s="1">
-        <v>15.13</v>
-      </c>
-      <c r="J39" s="1">
-        <v>15.6</v>
-      </c>
-      <c r="K39" s="1">
-        <v>15.82</v>
-      </c>
-      <c r="L39" s="1">
-        <v>16.03</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2201,37 +2198,37 @@
         <v>47300</v>
       </c>
       <c r="B40" s="1">
-        <v>22.43</v>
+        <v>24.08</v>
       </c>
       <c r="C40" s="1">
-        <v>21.71</v>
+        <v>23.36</v>
       </c>
       <c r="D40" s="1">
-        <v>20.87</v>
+        <v>22.52</v>
       </c>
       <c r="E40" s="1">
-        <v>18.7</v>
+        <v>20.350000000000001</v>
       </c>
       <c r="F40" s="1">
-        <v>17.350000000000001</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="G40" s="1">
-        <v>16.27</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="H40" s="1">
-        <v>15.88</v>
+        <v>17.53</v>
       </c>
       <c r="I40" s="1">
-        <v>15.32</v>
+        <v>16.97</v>
       </c>
       <c r="J40" s="1">
-        <v>15.46</v>
+        <v>17.11</v>
       </c>
       <c r="K40" s="1">
-        <v>15.62</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="L40" s="1">
-        <v>15.8</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2239,54 +2236,76 @@
         <v>10959</v>
       </c>
       <c r="B41" s="1">
-        <v>22.92</v>
+        <v>23.13</v>
       </c>
       <c r="C41" s="1">
-        <v>22.12</v>
+        <v>22.46</v>
       </c>
       <c r="D41" s="1">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E41" s="1">
-        <v>18.850000000000001</v>
+        <v>19.829999999999998</v>
       </c>
       <c r="F41" s="1">
-        <v>17.420000000000002</v>
+        <v>18.41</v>
       </c>
       <c r="G41" s="1">
+        <v>17.559999999999999</v>
+      </c>
+      <c r="H41" s="1">
+        <v>17.04</v>
+      </c>
+      <c r="I41" s="1">
+        <v>16.48</v>
+      </c>
+      <c r="J41" s="1">
+        <v>16.23</v>
+      </c>
+      <c r="K41" s="1">
+        <v>16.27</v>
+      </c>
+      <c r="L41" s="1">
+        <v>16.34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>11324</v>
+      </c>
+      <c r="B42" s="1">
+        <v>23.21</v>
+      </c>
+      <c r="C42" s="1">
+        <v>22.58</v>
+      </c>
+      <c r="D42" s="1">
+        <v>21.85</v>
+      </c>
+      <c r="E42" s="1">
+        <v>19.91</v>
+      </c>
+      <c r="F42" s="1">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="G42" s="1">
+        <v>17.63</v>
+      </c>
+      <c r="H42" s="1">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="I42" s="1">
+        <v>16.43</v>
+      </c>
+      <c r="J42" s="1">
         <v>16.32</v>
       </c>
-      <c r="H41" s="1">
-        <v>15.69</v>
-      </c>
-      <c r="I41" s="1">
-        <v>15.54</v>
-      </c>
-      <c r="J41" s="1">
-        <v>15.91</v>
-      </c>
-      <c r="K41" s="1">
-        <v>16.16</v>
-      </c>
-      <c r="L41" s="1">
-        <v>16.43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="K42" s="1">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="L42" s="1">
+        <v>16.39</v>
+      </c>
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
@@ -2304,7 +2323,7 @@
     </row>
     <row r="44" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2320,7 +2339,7 @@
     </row>
     <row r="45" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2336,7 +2355,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2351,7 +2370,9 @@
       <c r="L46" s="1"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A47" s="2"/>
+      <c r="A47" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -2365,7 +2386,9 @@
       <c r="L47" s="1"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -2380,7 +2403,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2394,38 +2417,6 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/ddeprofit.xlsx
+++ b/ddeprofit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E569AB47-5AE8-44BE-8FDC-FD752713BD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E96A321-7AF5-450D-9CF8-E600E4D792DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dde profit" sheetId="12" r:id="rId1"/>
@@ -360,49 +360,49 @@
       <ddeItem name="DOLINDEX.ABE" advise="1">
         <values>
           <value>
-            <val>100.306754</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.FEC" advise="1">
         <values>
           <value>
-            <val>100.304771</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MAX" advise="1">
         <values>
           <value>
-            <val>100.331935</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MIN" advise="1">
         <values>
           <value>
-            <val>100.27269699999999</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.NEG" advise="1">
         <values>
           <value>
-            <val>1689</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.ULT" advise="1">
         <values>
           <value>
-            <val>100.331935</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.VAR" advise="1">
         <values>
           <value>
-            <val>2.7081463552718787E-2</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
@@ -416,7 +416,7 @@
       <ddeItem name="DOLINDEX.VOL" advise="1">
         <values>
           <value>
-            <val>169426.927474</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
@@ -550,42 +550,42 @@
       <ddeItem name="USD/BRL.ABE" advise="1">
         <values>
           <value>
-            <val>5.3308999999999997</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.FEC" advise="1">
         <values>
           <value>
-            <val>5.3308999999999997</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MAX" advise="1">
         <values>
           <value>
-            <val>5.3308999999999997</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MIN" advise="1">
         <values>
           <value>
-            <val>5.3308999999999997</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.NEG" advise="1">
         <values>
           <value>
-            <val>2</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.ULT" advise="1">
         <values>
           <value>
-            <val>5.3308999999999997</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
@@ -606,7 +606,7 @@
       <ddeItem name="USD/BRL.VOL" advise="1">
         <values>
           <value>
-            <val>10.661799999999999</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
@@ -1101,23 +1101,23 @@
       </c>
       <c r="K4" cm="1">
         <f t="array" ref="K4">[1]!'USD/BRL.ULT'</f>
-        <v>5.3308999999999997</v>
+        <v>0</v>
       </c>
       <c r="L4" cm="1">
         <f t="array" ref="L4">[1]!'USD/BRL.ABE'</f>
-        <v>5.3308999999999997</v>
+        <v>0</v>
       </c>
       <c r="M4" cm="1">
         <f t="array" ref="M4">[1]!'USD/BRL.MAX'</f>
-        <v>5.3308999999999997</v>
+        <v>0</v>
       </c>
       <c r="N4" cm="1">
         <f t="array" ref="N4">[1]!'USD/BRL.MIN'</f>
-        <v>5.3308999999999997</v>
+        <v>0</v>
       </c>
       <c r="O4" cm="1">
         <f t="array" ref="O4">[1]!'USD/BRL.FEC'</f>
-        <v>5.3308999999999997</v>
+        <v>0</v>
       </c>
       <c r="P4" cm="1">
         <f t="array" ref="P4">[1]!'USD/BRL.VAR'</f>
@@ -1125,11 +1125,11 @@
       </c>
       <c r="Q4" cm="1">
         <f t="array" ref="Q4">[1]!'USD/BRL.NEG'</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" cm="1">
         <f t="array" ref="R4">[1]!'USD/BRL.VOL'</f>
-        <v>10.661799999999999</v>
+        <v>0</v>
       </c>
       <c r="S4" t="str" cm="1">
         <f t="array" ref="S4">[1]!'USD/BRL.VEN'</f>
@@ -1182,35 +1182,35 @@
       </c>
       <c r="K6" cm="1">
         <f t="array" ref="K6">[1]!DOLINDEX.ULT</f>
-        <v>100.331935</v>
+        <v>0</v>
       </c>
       <c r="L6" cm="1">
         <f t="array" ref="L6">[1]!DOLINDEX.ABE</f>
-        <v>100.306754</v>
+        <v>0</v>
       </c>
       <c r="M6" cm="1">
         <f t="array" ref="M6">[1]!DOLINDEX.MAX</f>
-        <v>100.331935</v>
+        <v>0</v>
       </c>
       <c r="N6" cm="1">
         <f t="array" ref="N6">[1]!DOLINDEX.MIN</f>
-        <v>100.27269699999999</v>
+        <v>0</v>
       </c>
       <c r="O6" cm="1">
         <f t="array" ref="O6">[1]!DOLINDEX.FEC</f>
-        <v>100.304771</v>
+        <v>0</v>
       </c>
       <c r="P6" cm="1">
         <f t="array" ref="P6">[1]!DOLINDEX.VAR</f>
-        <v>2.7081463552718787E-2</v>
+        <v>0</v>
       </c>
       <c r="Q6" cm="1">
         <f t="array" ref="Q6">[1]!DOLINDEX.NEG</f>
-        <v>1689</v>
+        <v>0</v>
       </c>
       <c r="R6" cm="1">
         <f t="array" ref="R6">[1]!DOLINDEX.VOL</f>
-        <v>169426.927474</v>
+        <v>0</v>
       </c>
       <c r="S6" t="str" cm="1">
         <f t="array" ref="S6">[1]!DOLINDEX.VEN</f>

--- a/ddeprofit.xlsx
+++ b/ddeprofit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E96A321-7AF5-450D-9CF8-E600E4D792DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1994F6F2-7998-466A-AC4C-3B92ADF8F278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -360,49 +360,49 @@
       <ddeItem name="DOLINDEX.ABE" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>100.34394399999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.FEC" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>100.344807</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MAX" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>100.34394399999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MIN" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>100.180021</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.NEG" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>979</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.ULT" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>100.273634</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.VAR" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>-7.0928433795273804E-2</val>
           </value>
         </values>
       </ddeItem>
@@ -416,7 +416,7 @@
       <ddeItem name="DOLINDEX.VOL" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>98139.869485000003</val>
           </value>
         </values>
       </ddeItem>
@@ -550,49 +550,49 @@
       <ddeItem name="USD/BRL.ABE" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>5.3302620000000003</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.FEC" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>5.3302620000000003</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MAX" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>5.3336110000000003</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MIN" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>5.3252490000000003</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.NEG" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>95</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.ULT" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>5.3277000000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.VAR" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>-4.8065179535271341E-2</val>
           </value>
         </values>
       </ddeItem>
@@ -606,7 +606,7 @@
       <ddeItem name="USD/BRL.VOL" advise="1">
         <values>
           <value>
-            <val>0</val>
+            <val>506.33307600000001</val>
           </value>
         </values>
       </ddeItem>
@@ -1101,35 +1101,35 @@
       </c>
       <c r="K4" cm="1">
         <f t="array" ref="K4">[1]!'USD/BRL.ULT'</f>
-        <v>0</v>
+        <v>5.3277000000000001</v>
       </c>
       <c r="L4" cm="1">
         <f t="array" ref="L4">[1]!'USD/BRL.ABE'</f>
-        <v>0</v>
+        <v>5.3302620000000003</v>
       </c>
       <c r="M4" cm="1">
         <f t="array" ref="M4">[1]!'USD/BRL.MAX'</f>
-        <v>0</v>
+        <v>5.3336110000000003</v>
       </c>
       <c r="N4" cm="1">
         <f t="array" ref="N4">[1]!'USD/BRL.MIN'</f>
-        <v>0</v>
+        <v>5.3252490000000003</v>
       </c>
       <c r="O4" cm="1">
         <f t="array" ref="O4">[1]!'USD/BRL.FEC'</f>
-        <v>0</v>
+        <v>5.3302620000000003</v>
       </c>
       <c r="P4" cm="1">
         <f t="array" ref="P4">[1]!'USD/BRL.VAR'</f>
-        <v>0</v>
+        <v>-4.8065179535271341E-2</v>
       </c>
       <c r="Q4" cm="1">
         <f t="array" ref="Q4">[1]!'USD/BRL.NEG'</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R4" cm="1">
         <f t="array" ref="R4">[1]!'USD/BRL.VOL'</f>
-        <v>0</v>
+        <v>506.33307600000001</v>
       </c>
       <c r="S4" t="str" cm="1">
         <f t="array" ref="S4">[1]!'USD/BRL.VEN'</f>
@@ -1182,35 +1182,35 @@
       </c>
       <c r="K6" cm="1">
         <f t="array" ref="K6">[1]!DOLINDEX.ULT</f>
-        <v>0</v>
+        <v>100.273634</v>
       </c>
       <c r="L6" cm="1">
         <f t="array" ref="L6">[1]!DOLINDEX.ABE</f>
-        <v>0</v>
+        <v>100.34394399999999</v>
       </c>
       <c r="M6" cm="1">
         <f t="array" ref="M6">[1]!DOLINDEX.MAX</f>
-        <v>0</v>
+        <v>100.34394399999999</v>
       </c>
       <c r="N6" cm="1">
         <f t="array" ref="N6">[1]!DOLINDEX.MIN</f>
-        <v>0</v>
+        <v>100.180021</v>
       </c>
       <c r="O6" cm="1">
         <f t="array" ref="O6">[1]!DOLINDEX.FEC</f>
-        <v>0</v>
+        <v>100.344807</v>
       </c>
       <c r="P6" cm="1">
         <f t="array" ref="P6">[1]!DOLINDEX.VAR</f>
-        <v>0</v>
+        <v>-7.0928433795273804E-2</v>
       </c>
       <c r="Q6" cm="1">
         <f t="array" ref="Q6">[1]!DOLINDEX.NEG</f>
-        <v>0</v>
+        <v>979</v>
       </c>
       <c r="R6" cm="1">
         <f t="array" ref="R6">[1]!DOLINDEX.VOL</f>
-        <v>0</v>
+        <v>98139.869485000003</v>
       </c>
       <c r="S6" t="str" cm="1">
         <f t="array" ref="S6">[1]!DOLINDEX.VEN</f>

--- a/ddeprofit.xlsx
+++ b/ddeprofit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1994F6F2-7998-466A-AC4C-3B92ADF8F278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE06337-0B3E-4657-AC2A-9EFD0D1E8FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="superficie_de_volatilidade_de_dolar" localSheetId="1">base_b3!$A$1:$L$49</definedName>
+    <definedName name="superficie_de_volatilidade_de_dolar" localSheetId="1">base_b3!$A$1:$L$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -178,9 +178,6 @@
     <t>Delta %</t>
   </si>
   <si>
-    <t xml:space="preserve">         Atualizado em: 13/03/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve"> * A superfície de volatilidade de dólar é construída com base nas informações coletadas por um pool de Informantes às 18h</t>
   </si>
   <si>
@@ -188,6 +185,9 @@
   </si>
   <si>
     <t xml:space="preserve">                                                                                                                                                                                                               Download do arquivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         Atualizado em: 16/03/2026</t>
   </si>
 </sst>
 </file>
@@ -297,49 +297,49 @@
       <ddeItem name="DI1FUT.ABE" advise="1">
         <values>
           <value>
-            <val>13.455</val>
+            <val>13.73</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.FEC" advise="1">
         <values>
           <value>
-            <val>13.525</val>
+            <val>13.930000000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.MAX" advise="1">
         <values>
           <value>
-            <val>13.994999999999999</val>
+            <val>13.734999999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.MIN" advise="1">
         <values>
           <value>
-            <val>13.37</val>
+            <val>13.51</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.NEG" advise="1">
         <values>
           <value>
-            <val>117314</val>
+            <val>74403</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.ULT" advise="1">
         <values>
           <value>
-            <val>13.93</val>
+            <val>13.535</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.VAR" advise="1">
         <values>
           <value>
-            <val>2.9944547134935391</val>
+            <val>-2.835606604450831</val>
           </value>
         </values>
       </ddeItem>
@@ -353,56 +353,56 @@
       <ddeItem name="DI1FUT.VOL" advise="1">
         <values>
           <value>
-            <val>95560612851.149994</val>
+            <val>60485327161.019997</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.ABE" advise="1">
         <values>
           <value>
-            <val>100.34394399999999</val>
+            <val>99.858219000000005</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.FEC" advise="1">
         <values>
           <value>
-            <val>100.344807</val>
+            <val>99.857467999999997</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MAX" advise="1">
         <values>
           <value>
-            <val>100.34394399999999</val>
+            <val>100.111442</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MIN" advise="1">
         <values>
           <value>
-            <val>100.180021</val>
+            <val>99.673192</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.NEG" advise="1">
         <values>
           <value>
-            <val>979</val>
+            <val>7390</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.ULT" advise="1">
         <values>
           <value>
-            <val>100.273634</val>
+            <val>99.800200000000004</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.VAR" advise="1">
         <values>
           <value>
-            <val>-7.0928433795273804E-2</val>
+            <val>-5.7349741733887072E-2</val>
           </value>
         </values>
       </ddeItem>
@@ -416,56 +416,56 @@
       <ddeItem name="DOLINDEX.VOL" advise="1">
         <values>
           <value>
-            <val>98139.869485000003</val>
+            <val>738213.01773199998</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.ABE" advise="1">
         <values>
           <value>
-            <val>22.2</val>
+            <val>20.6</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.FEC" advise="1">
         <values>
           <value>
-            <val>23.900000000000002</val>
+            <val>22.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.MAX" advise="1">
         <values>
           <value>
-            <val>23.5</val>
+            <val>20.9</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.MIN" advise="1">
         <values>
           <value>
-            <val>21.9</val>
+            <val>19.8</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.NEG" advise="1">
         <values>
           <value>
-            <val>114</val>
+            <val>174</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.ULT" advise="1">
         <values>
           <value>
-            <val>22.5</val>
+            <val>20.3</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.VAR" advise="1">
         <values>
           <value>
-            <val>-5.8577405857740672</val>
+            <val>-9.7777777777777715</val>
           </value>
         </values>
       </ddeItem>
@@ -479,56 +479,56 @@
       <ddeItem name="FRP0.VOL" advise="1">
         <values>
           <value>
-            <val>4289965750</val>
+            <val>7131245550</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.ABE" advise="1">
         <values>
           <value>
-            <val>5148.75</val>
+            <val>5032</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.FEC" advise="1">
         <values>
           <value>
-            <val>5112.75</val>
+            <val>5048.25</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.MAX" advise="1">
         <values>
           <value>
-            <val>5153</val>
+            <val>5069.25</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.MIN" advise="1">
         <values>
           <value>
-            <val>5046.75</val>
+            <val>5011.75</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.NEG" advise="1">
         <values>
           <value>
-            <val>839</val>
+            <val>784</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.ULT" advise="1">
         <values>
           <value>
-            <val>5048.25</val>
+            <val>5043.75</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.VAR" advise="1">
         <values>
           <value>
-            <val>-1.2615520023470737</val>
+            <val>-8.9139800921117285E-2</val>
           </value>
         </values>
       </ddeItem>
@@ -542,7 +542,7 @@
       <ddeItem name="GLDFUT.VOL" advise="1">
         <values>
           <value>
-            <val>63473095.75</val>
+            <val>48905578.57</val>
           </value>
         </values>
       </ddeItem>
@@ -550,49 +550,49 @@
       <ddeItem name="USD/BRL.ABE" advise="1">
         <values>
           <value>
-            <val>5.3302620000000003</val>
+            <val>5.2314999999999996</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.FEC" advise="1">
         <values>
           <value>
-            <val>5.3302620000000003</val>
+            <val>5.2332999999999998</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MAX" advise="1">
         <values>
           <value>
-            <val>5.3336110000000003</val>
+            <val>5.2504340000000003</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MIN" advise="1">
         <values>
           <value>
-            <val>5.3252490000000003</val>
+            <val>5.2304909999999998</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.NEG" advise="1">
         <values>
           <value>
-            <val>95</val>
+            <val>915</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.ULT" advise="1">
         <values>
           <value>
-            <val>5.3277000000000001</val>
+            <val>5.2481999999999998</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.VAR" advise="1">
         <values>
           <value>
-            <val>-4.8065179535271341E-2</val>
+            <val>0.28471518926870942</val>
           </value>
         </values>
       </ddeItem>
@@ -606,49 +606,49 @@
       <ddeItem name="USD/BRL.VOL" advise="1">
         <values>
           <value>
-            <val>506.33307600000001</val>
+            <val>4790.514013</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.ABE" advise="1">
         <values>
           <value>
-            <val>5262</val>
+            <val>5304.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.MAX" advise="1">
         <values>
           <value>
-            <val>5358.5</val>
+            <val>5306.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.MIN" advise="1">
         <values>
           <value>
-            <val>5237.5</val>
+            <val>5246</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.NEG" advise="1">
         <values>
           <value>
-            <val>967342</val>
+            <val>707229</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.ULT" advise="1">
         <values>
           <value>
-            <val>5354</val>
+            <val>5252.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.VAR" advise="1">
         <values>
           <value>
-            <val>1.382313955690222</val>
+            <val>-1.8957788569293967</val>
           </value>
         </values>
       </ddeItem>
@@ -662,7 +662,7 @@
       <ddeItem name="WDOFUT.VOL" advise="1">
         <values>
           <value>
-            <val>200213358680</val>
+            <val>142113673710</val>
           </value>
         </values>
       </ddeItem>
@@ -1019,35 +1019,35 @@
       </c>
       <c r="K2" cm="1">
         <f t="array" ref="K2">[1]!DI1FUT.ULT</f>
-        <v>13.93</v>
+        <v>13.535</v>
       </c>
       <c r="L2" cm="1">
         <f t="array" ref="L2">[1]!DI1FUT.ABE</f>
-        <v>13.455</v>
+        <v>13.73</v>
       </c>
       <c r="M2" cm="1">
         <f t="array" ref="M2">[1]!DI1FUT.MAX</f>
-        <v>13.994999999999999</v>
+        <v>13.734999999999999</v>
       </c>
       <c r="N2" cm="1">
         <f t="array" ref="N2">[1]!DI1FUT.MIN</f>
-        <v>13.37</v>
+        <v>13.51</v>
       </c>
       <c r="O2" cm="1">
         <f t="array" ref="O2">[1]!DI1FUT.FEC</f>
-        <v>13.525</v>
+        <v>13.930000000000001</v>
       </c>
       <c r="P2" cm="1">
         <f t="array" ref="P2">[1]!DI1FUT.VAR</f>
-        <v>2.9944547134935391</v>
+        <v>-2.835606604450831</v>
       </c>
       <c r="Q2" cm="1">
         <f t="array" ref="Q2">[1]!DI1FUT.NEG</f>
-        <v>117314</v>
+        <v>74403</v>
       </c>
       <c r="R2" cm="1">
         <f t="array" ref="R2">[1]!DI1FUT.VOL</f>
-        <v>95560612851.149994</v>
+        <v>60485327161.019997</v>
       </c>
       <c r="S2" t="str" cm="1">
         <f t="array" ref="S2">[1]!DI1FUT.VEN</f>
@@ -1060,35 +1060,35 @@
       </c>
       <c r="K3" cm="1">
         <f t="array" ref="K3">[1]!FRP0.ULT</f>
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="L3" cm="1">
         <f t="array" ref="L3">[1]!FRP0.ABE</f>
-        <v>22.2</v>
+        <v>20.6</v>
       </c>
       <c r="M3" cm="1">
         <f t="array" ref="M3">[1]!FRP0.MAX</f>
-        <v>23.5</v>
+        <v>20.9</v>
       </c>
       <c r="N3" cm="1">
         <f t="array" ref="N3">[1]!FRP0.MIN</f>
-        <v>21.9</v>
+        <v>19.8</v>
       </c>
       <c r="O3" cm="1">
         <f t="array" ref="O3">[1]!FRP0.FEC</f>
-        <v>23.900000000000002</v>
+        <v>22.5</v>
       </c>
       <c r="P3" cm="1">
         <f t="array" ref="P3">[1]!FRP0.VAR</f>
-        <v>-5.8577405857740672</v>
+        <v>-9.7777777777777715</v>
       </c>
       <c r="Q3" cm="1">
         <f t="array" ref="Q3">[1]!FRP0.NEG</f>
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="R3" cm="1">
         <f t="array" ref="R3">[1]!FRP0.VOL</f>
-        <v>4289965750</v>
+        <v>7131245550</v>
       </c>
       <c r="S3" t="str" cm="1">
         <f t="array" ref="S3">[1]!FRP0.VEN</f>
@@ -1101,35 +1101,35 @@
       </c>
       <c r="K4" cm="1">
         <f t="array" ref="K4">[1]!'USD/BRL.ULT'</f>
-        <v>5.3277000000000001</v>
+        <v>5.2481999999999998</v>
       </c>
       <c r="L4" cm="1">
         <f t="array" ref="L4">[1]!'USD/BRL.ABE'</f>
-        <v>5.3302620000000003</v>
+        <v>5.2314999999999996</v>
       </c>
       <c r="M4" cm="1">
         <f t="array" ref="M4">[1]!'USD/BRL.MAX'</f>
-        <v>5.3336110000000003</v>
+        <v>5.2504340000000003</v>
       </c>
       <c r="N4" cm="1">
         <f t="array" ref="N4">[1]!'USD/BRL.MIN'</f>
-        <v>5.3252490000000003</v>
+        <v>5.2304909999999998</v>
       </c>
       <c r="O4" cm="1">
         <f t="array" ref="O4">[1]!'USD/BRL.FEC'</f>
-        <v>5.3302620000000003</v>
+        <v>5.2332999999999998</v>
       </c>
       <c r="P4" cm="1">
         <f t="array" ref="P4">[1]!'USD/BRL.VAR'</f>
-        <v>-4.8065179535271341E-2</v>
+        <v>0.28471518926870942</v>
       </c>
       <c r="Q4" cm="1">
         <f t="array" ref="Q4">[1]!'USD/BRL.NEG'</f>
-        <v>95</v>
+        <v>915</v>
       </c>
       <c r="R4" cm="1">
         <f t="array" ref="R4">[1]!'USD/BRL.VOL'</f>
-        <v>506.33307600000001</v>
+        <v>4790.514013</v>
       </c>
       <c r="S4" t="str" cm="1">
         <f t="array" ref="S4">[1]!'USD/BRL.VEN'</f>
@@ -1142,34 +1142,34 @@
       </c>
       <c r="K5" cm="1">
         <f t="array" ref="K5">[1]!WDOFUT.ULT</f>
-        <v>5354</v>
+        <v>5252.5</v>
       </c>
       <c r="L5" cm="1">
         <f t="array" ref="L5">[1]!WDOFUT.ABE</f>
-        <v>5262</v>
+        <v>5304.5</v>
       </c>
       <c r="M5" cm="1">
         <f t="array" ref="M5">[1]!WDOFUT.MAX</f>
-        <v>5358.5</v>
+        <v>5306.5</v>
       </c>
       <c r="N5" cm="1">
         <f t="array" ref="N5">[1]!WDOFUT.MIN</f>
-        <v>5237.5</v>
+        <v>5246</v>
       </c>
       <c r="O5">
         <v>5339.5</v>
       </c>
       <c r="P5" cm="1">
         <f t="array" ref="P5">[1]!WDOFUT.VAR</f>
-        <v>1.382313955690222</v>
+        <v>-1.8957788569293967</v>
       </c>
       <c r="Q5" cm="1">
         <f t="array" ref="Q5">[1]!WDOFUT.NEG</f>
-        <v>967342</v>
+        <v>707229</v>
       </c>
       <c r="R5" cm="1">
         <f t="array" ref="R5">[1]!WDOFUT.VOL</f>
-        <v>200213358680</v>
+        <v>142113673710</v>
       </c>
       <c r="S5" t="str" cm="1">
         <f t="array" ref="S5">[1]!WDOFUT.VEN</f>
@@ -1182,35 +1182,35 @@
       </c>
       <c r="K6" cm="1">
         <f t="array" ref="K6">[1]!DOLINDEX.ULT</f>
-        <v>100.273634</v>
+        <v>99.800200000000004</v>
       </c>
       <c r="L6" cm="1">
         <f t="array" ref="L6">[1]!DOLINDEX.ABE</f>
-        <v>100.34394399999999</v>
+        <v>99.858219000000005</v>
       </c>
       <c r="M6" cm="1">
         <f t="array" ref="M6">[1]!DOLINDEX.MAX</f>
-        <v>100.34394399999999</v>
+        <v>100.111442</v>
       </c>
       <c r="N6" cm="1">
         <f t="array" ref="N6">[1]!DOLINDEX.MIN</f>
-        <v>100.180021</v>
+        <v>99.673192</v>
       </c>
       <c r="O6" cm="1">
         <f t="array" ref="O6">[1]!DOLINDEX.FEC</f>
-        <v>100.344807</v>
+        <v>99.857467999999997</v>
       </c>
       <c r="P6" cm="1">
         <f t="array" ref="P6">[1]!DOLINDEX.VAR</f>
-        <v>-7.0928433795273804E-2</v>
+        <v>-5.7349741733887072E-2</v>
       </c>
       <c r="Q6" cm="1">
         <f t="array" ref="Q6">[1]!DOLINDEX.NEG</f>
-        <v>979</v>
+        <v>7390</v>
       </c>
       <c r="R6" cm="1">
         <f t="array" ref="R6">[1]!DOLINDEX.VOL</f>
-        <v>98139.869485000003</v>
+        <v>738213.01773199998</v>
       </c>
       <c r="S6" t="str" cm="1">
         <f t="array" ref="S6">[1]!DOLINDEX.VEN</f>
@@ -1223,35 +1223,35 @@
       </c>
       <c r="K7" cm="1">
         <f t="array" ref="K7">[1]!GLDFUT.ULT</f>
-        <v>5048.25</v>
+        <v>5043.75</v>
       </c>
       <c r="L7" cm="1">
         <f t="array" ref="L7">[1]!GLDFUT.ABE</f>
-        <v>5148.75</v>
+        <v>5032</v>
       </c>
       <c r="M7" cm="1">
         <f t="array" ref="M7">[1]!GLDFUT.MAX</f>
-        <v>5153</v>
+        <v>5069.25</v>
       </c>
       <c r="N7" cm="1">
         <f t="array" ref="N7">[1]!GLDFUT.MIN</f>
-        <v>5046.75</v>
+        <v>5011.75</v>
       </c>
       <c r="O7" cm="1">
         <f t="array" ref="O7">[1]!GLDFUT.FEC</f>
-        <v>5112.75</v>
+        <v>5048.25</v>
       </c>
       <c r="P7" cm="1">
         <f t="array" ref="P7">[1]!GLDFUT.VAR</f>
-        <v>-1.2615520023470737</v>
+        <v>-8.9139800921117285E-2</v>
       </c>
       <c r="Q7" cm="1">
         <f t="array" ref="Q7">[1]!GLDFUT.NEG</f>
-        <v>839</v>
+        <v>784</v>
       </c>
       <c r="R7" cm="1">
         <f t="array" ref="R7">[1]!GLDFUT.VOL</f>
-        <v>63473095.75</v>
+        <v>48905578.57</v>
       </c>
       <c r="S7" t="str" cm="1">
         <f t="array" ref="S7">[1]!GLDFUT.VEN</f>
@@ -1266,7 +1266,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Planilha10"/>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="5" customWidth="1"/>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1400,37 +1400,37 @@
         <v>46113</v>
       </c>
       <c r="B19" s="4">
-        <v>20.98</v>
+        <v>21.99</v>
       </c>
       <c r="C19" s="4">
-        <v>20.38</v>
+        <v>20.97</v>
       </c>
       <c r="D19" s="4">
-        <v>19.600000000000001</v>
+        <v>19.84</v>
       </c>
       <c r="E19" s="4">
-        <v>17.02</v>
+        <v>17.34</v>
       </c>
       <c r="F19" s="4">
-        <v>15.67</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="G19" s="4">
-        <v>14.69</v>
+        <v>15.09</v>
       </c>
       <c r="H19" s="4">
-        <v>13.9</v>
+        <v>14.34</v>
       </c>
       <c r="I19" s="4">
-        <v>13.1</v>
+        <v>13.59</v>
       </c>
       <c r="J19" s="4">
-        <v>12.42</v>
+        <v>12.98</v>
       </c>
       <c r="K19" s="4">
-        <v>13.44</v>
+        <v>14.01</v>
       </c>
       <c r="L19" s="4">
-        <v>15.12</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1438,37 +1438,37 @@
         <v>46143</v>
       </c>
       <c r="B20" s="4">
-        <v>21.16</v>
+        <v>21.46</v>
       </c>
       <c r="C20" s="4">
-        <v>20.5</v>
+        <v>20.71</v>
       </c>
       <c r="D20" s="4">
-        <v>19.649999999999999</v>
+        <v>19.79</v>
       </c>
       <c r="E20" s="4">
-        <v>16.95</v>
+        <v>17.13</v>
       </c>
       <c r="F20" s="4">
-        <v>15.55</v>
+        <v>15.75</v>
       </c>
       <c r="G20" s="4">
-        <v>14.5</v>
+        <v>14.73</v>
       </c>
       <c r="H20" s="4">
-        <v>13.71</v>
+        <v>13.96</v>
       </c>
       <c r="I20" s="4">
-        <v>12.88</v>
+        <v>13.14</v>
       </c>
       <c r="J20" s="4">
-        <v>12.21</v>
+        <v>12.51</v>
       </c>
       <c r="K20" s="4">
-        <v>12.06</v>
+        <v>12.5</v>
       </c>
       <c r="L20" s="4">
-        <v>11.96</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1476,37 +1476,37 @@
         <v>46174</v>
       </c>
       <c r="B21" s="4">
-        <v>20.75</v>
+        <v>21.4</v>
       </c>
       <c r="C21" s="4">
-        <v>19.97</v>
+        <v>20.47</v>
       </c>
       <c r="D21" s="4">
-        <v>19.04</v>
+        <v>19.420000000000002</v>
       </c>
       <c r="E21" s="4">
-        <v>16.559999999999999</v>
+        <v>16.95</v>
       </c>
       <c r="F21" s="4">
-        <v>15.28</v>
+        <v>15.9</v>
       </c>
       <c r="G21" s="4">
-        <v>14.34</v>
+        <v>14.73</v>
       </c>
       <c r="H21" s="4">
-        <v>13.65</v>
+        <v>14.04</v>
       </c>
       <c r="I21" s="4">
-        <v>12.91</v>
+        <v>13.3</v>
       </c>
       <c r="J21" s="4">
-        <v>12.38</v>
+        <v>12.77</v>
       </c>
       <c r="K21" s="4">
-        <v>12.25</v>
+        <v>12.79</v>
       </c>
       <c r="L21" s="4">
-        <v>12.17</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1514,37 +1514,37 @@
         <v>46204</v>
       </c>
       <c r="B22" s="4">
-        <v>20.92</v>
+        <v>21.47</v>
       </c>
       <c r="C22" s="4">
-        <v>20.09</v>
+        <v>20.52</v>
       </c>
       <c r="D22" s="4">
-        <v>19.12</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="E22" s="4">
-        <v>16.62</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="F22" s="4">
-        <v>15.6</v>
+        <v>15.88</v>
       </c>
       <c r="G22" s="4">
-        <v>14.41</v>
+        <v>14.72</v>
       </c>
       <c r="H22" s="4">
-        <v>13.74</v>
+        <v>14.06</v>
       </c>
       <c r="I22" s="4">
+        <v>13.36</v>
+      </c>
+      <c r="J22" s="4">
+        <v>12.91</v>
+      </c>
+      <c r="K22" s="4">
+        <v>12.97</v>
+      </c>
+      <c r="L22" s="4">
         <v>13.05</v>
-      </c>
-      <c r="J22" s="4">
-        <v>12.61</v>
-      </c>
-      <c r="K22" s="4">
-        <v>12.55</v>
-      </c>
-      <c r="L22" s="4">
-        <v>12.52</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1552,37 +1552,37 @@
         <v>46235</v>
       </c>
       <c r="B23" s="4">
-        <v>20.8</v>
+        <v>21.16</v>
       </c>
       <c r="C23" s="4">
-        <v>19.989999999999998</v>
+        <v>20.25</v>
       </c>
       <c r="D23" s="4">
-        <v>19.05</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="E23" s="4">
-        <v>16.66</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="F23" s="4">
-        <v>15.64</v>
+        <v>15.81</v>
       </c>
       <c r="G23" s="4">
-        <v>14.5</v>
+        <v>14.69</v>
       </c>
       <c r="H23" s="4">
-        <v>13.87</v>
+        <v>14.05</v>
       </c>
       <c r="I23" s="4">
-        <v>13.21</v>
+        <v>13.39</v>
       </c>
       <c r="J23" s="4">
-        <v>12.83</v>
+        <v>13.01</v>
       </c>
       <c r="K23" s="4">
-        <v>12.79</v>
+        <v>13.05</v>
       </c>
       <c r="L23" s="4">
-        <v>12.77</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1590,37 +1590,37 @@
         <v>46266</v>
       </c>
       <c r="B24" s="4">
-        <v>20.66</v>
+        <v>20.96</v>
       </c>
       <c r="C24" s="4">
-        <v>19.88</v>
+        <v>20.12</v>
       </c>
       <c r="D24" s="4">
-        <v>18.989999999999998</v>
+        <v>19.16</v>
       </c>
       <c r="E24" s="4">
-        <v>16.690000000000001</v>
+        <v>16.86</v>
       </c>
       <c r="F24" s="4">
-        <v>15.68</v>
+        <v>15.84</v>
       </c>
       <c r="G24" s="4">
-        <v>14.58</v>
+        <v>14.75</v>
       </c>
       <c r="H24" s="4">
-        <v>13.97</v>
+        <v>14.15</v>
       </c>
       <c r="I24" s="4">
-        <v>13.35</v>
+        <v>13.52</v>
       </c>
       <c r="J24" s="4">
-        <v>13.04</v>
+        <v>13.21</v>
       </c>
       <c r="K24" s="4">
-        <v>13</v>
+        <v>13.24</v>
       </c>
       <c r="L24" s="4">
-        <v>12.98</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1628,37 +1628,37 @@
         <v>46296</v>
       </c>
       <c r="B25" s="4">
-        <v>20.92</v>
+        <v>21.08</v>
       </c>
       <c r="C25" s="4">
-        <v>20.22</v>
+        <v>20.329999999999998</v>
       </c>
       <c r="D25" s="4">
-        <v>19.38</v>
+        <v>19.45</v>
       </c>
       <c r="E25" s="4">
-        <v>17.03</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="F25" s="4">
-        <v>16</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="G25" s="4">
-        <v>14.83</v>
+        <v>14.96</v>
       </c>
       <c r="H25" s="4">
-        <v>14.28</v>
+        <v>14.35</v>
       </c>
       <c r="I25" s="4">
-        <v>13.67</v>
+        <v>13.74</v>
       </c>
       <c r="J25" s="4">
-        <v>13.41</v>
+        <v>13.48</v>
       </c>
       <c r="K25" s="4">
-        <v>13.38</v>
+        <v>13.5</v>
       </c>
       <c r="L25" s="4">
-        <v>13.36</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1666,37 +1666,37 @@
         <v>46327</v>
       </c>
       <c r="B26" s="4">
-        <v>21.32</v>
+        <v>21.34</v>
       </c>
       <c r="C26" s="4">
-        <v>20.64</v>
+        <v>20.65</v>
       </c>
       <c r="D26" s="4">
-        <v>19.79</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="E26" s="4">
-        <v>17.38</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="F26" s="4">
-        <v>16.13</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="G26" s="4">
-        <v>15.23</v>
+        <v>15.25</v>
       </c>
       <c r="H26" s="4">
-        <v>14.64</v>
+        <v>14.66</v>
       </c>
       <c r="I26" s="4">
-        <v>14</v>
+        <v>14.02</v>
       </c>
       <c r="J26" s="4">
-        <v>13.73</v>
+        <v>13.76</v>
       </c>
       <c r="K26" s="4">
-        <v>13.77</v>
+        <v>13.79</v>
       </c>
       <c r="L26" s="4">
-        <v>13.84</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1704,37 +1704,37 @@
         <v>46357</v>
       </c>
       <c r="B27" s="4">
-        <v>21.38</v>
+        <v>21.28</v>
       </c>
       <c r="C27" s="4">
-        <v>20.77</v>
+        <v>20.64</v>
       </c>
       <c r="D27" s="4">
-        <v>20.03</v>
+        <v>19.89</v>
       </c>
       <c r="E27" s="4">
-        <v>17.989999999999998</v>
+        <v>17.89</v>
       </c>
       <c r="F27" s="4">
-        <v>16.690000000000001</v>
+        <v>16.37</v>
       </c>
       <c r="G27" s="4">
-        <v>15.61</v>
+        <v>15.5</v>
       </c>
       <c r="H27" s="4">
-        <v>14.77</v>
+        <v>14.66</v>
       </c>
       <c r="I27" s="4">
-        <v>14.29</v>
+        <v>14.19</v>
       </c>
       <c r="J27" s="4">
-        <v>14.27</v>
+        <v>14.17</v>
       </c>
       <c r="K27" s="4">
-        <v>14.21</v>
+        <v>14.11</v>
       </c>
       <c r="L27" s="4">
-        <v>14.13</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1742,37 +1742,37 @@
         <v>46388</v>
       </c>
       <c r="B28" s="4">
-        <v>21.31</v>
+        <v>21.22</v>
       </c>
       <c r="C28" s="4">
-        <v>20.68</v>
+        <v>20.58</v>
       </c>
       <c r="D28" s="4">
-        <v>19.91</v>
+        <v>19.8</v>
       </c>
       <c r="E28" s="4">
-        <v>17.690000000000001</v>
+        <v>17.579999999999998</v>
       </c>
       <c r="F28" s="4">
-        <v>16.739999999999998</v>
+        <v>16.64</v>
       </c>
       <c r="G28" s="4">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="H28" s="4">
-        <v>15.16</v>
+        <v>15.05</v>
       </c>
       <c r="I28" s="4">
-        <v>14.63</v>
+        <v>14.53</v>
       </c>
       <c r="J28" s="4">
-        <v>14.48</v>
+        <v>14.38</v>
       </c>
       <c r="K28" s="4">
-        <v>14.4</v>
+        <v>14.31</v>
       </c>
       <c r="L28" s="4">
-        <v>14.33</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1783,25 +1783,25 @@
         <v>21.33</v>
       </c>
       <c r="C29" s="4">
-        <v>20.65</v>
+        <v>20.64</v>
       </c>
       <c r="D29" s="4">
         <v>19.850000000000001</v>
       </c>
       <c r="E29" s="4">
-        <v>17.850000000000001</v>
+        <v>17.84</v>
       </c>
       <c r="F29" s="4">
-        <v>16.350000000000001</v>
+        <v>16.34</v>
       </c>
       <c r="G29" s="4">
         <v>15.48</v>
       </c>
       <c r="H29" s="4">
-        <v>14.93</v>
+        <v>14.92</v>
       </c>
       <c r="I29" s="4">
-        <v>14.33</v>
+        <v>14.32</v>
       </c>
       <c r="J29" s="4">
         <v>14.1</v>
@@ -1810,7 +1810,7 @@
         <v>14.14</v>
       </c>
       <c r="L29" s="4">
-        <v>14.21</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1818,37 +1818,37 @@
         <v>46447</v>
       </c>
       <c r="B30" s="4">
-        <v>21.23</v>
+        <v>21.3</v>
       </c>
       <c r="C30" s="4">
-        <v>20.56</v>
+        <v>20.62</v>
       </c>
       <c r="D30" s="4">
-        <v>19.78</v>
+        <v>19.84</v>
       </c>
       <c r="E30" s="4">
-        <v>17.82</v>
+        <v>17.88</v>
       </c>
       <c r="F30" s="4">
-        <v>16.36</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="G30" s="4">
-        <v>15.51</v>
+        <v>15.57</v>
       </c>
       <c r="H30" s="4">
-        <v>14.98</v>
+        <v>15.04</v>
       </c>
       <c r="I30" s="4">
-        <v>14.39</v>
+        <v>14.45</v>
       </c>
       <c r="J30" s="4">
-        <v>14.19</v>
+        <v>14.25</v>
       </c>
       <c r="K30" s="4">
-        <v>14.23</v>
+        <v>14.29</v>
       </c>
       <c r="L30" s="4">
-        <v>14.29</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1856,37 +1856,37 @@
         <v>46478</v>
       </c>
       <c r="B31" s="4">
-        <v>20.75</v>
+        <v>20.73</v>
       </c>
       <c r="C31" s="4">
-        <v>20.239999999999998</v>
+        <v>20.18</v>
       </c>
       <c r="D31" s="4">
-        <v>19.59</v>
+        <v>19.510000000000002</v>
       </c>
       <c r="E31" s="4">
-        <v>17.7</v>
+        <v>17.62</v>
       </c>
       <c r="F31" s="4">
-        <v>16.37</v>
+        <v>16.29</v>
       </c>
       <c r="G31" s="4">
-        <v>15.54</v>
+        <v>15.46</v>
       </c>
       <c r="H31" s="4">
-        <v>15.05</v>
+        <v>14.97</v>
       </c>
       <c r="I31" s="4">
-        <v>14.6</v>
+        <v>14.52</v>
       </c>
       <c r="J31" s="4">
-        <v>14.62</v>
+        <v>14.54</v>
       </c>
       <c r="K31" s="4">
-        <v>14.53</v>
+        <v>14.48</v>
       </c>
       <c r="L31" s="4">
-        <v>14.39</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1894,37 +1894,37 @@
         <v>46569</v>
       </c>
       <c r="B32" s="4">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="C32" s="4">
-        <v>20.65</v>
+        <v>20.64</v>
       </c>
       <c r="D32" s="4">
-        <v>19.920000000000002</v>
+        <v>19.89</v>
       </c>
       <c r="E32" s="4">
-        <v>18.12</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="F32" s="4">
-        <v>16.760000000000002</v>
+        <v>16.73</v>
       </c>
       <c r="G32" s="4">
-        <v>15.99</v>
+        <v>15.97</v>
       </c>
       <c r="H32" s="4">
-        <v>15.53</v>
+        <v>15.5</v>
       </c>
       <c r="I32" s="4">
-        <v>15.07</v>
+        <v>15.05</v>
       </c>
       <c r="J32" s="4">
-        <v>15.02</v>
+        <v>14.99</v>
       </c>
       <c r="K32" s="4">
-        <v>15.02</v>
+        <v>15.01</v>
       </c>
       <c r="L32" s="4">
-        <v>15.02</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2008,37 +2008,37 @@
         <v>46753</v>
       </c>
       <c r="B35" s="1">
-        <v>21.72</v>
+        <v>21.78</v>
       </c>
       <c r="C35" s="1">
-        <v>21.1</v>
+        <v>21.16</v>
       </c>
       <c r="D35" s="1">
-        <v>20.350000000000001</v>
+        <v>20.41</v>
       </c>
       <c r="E35" s="1">
-        <v>18.28</v>
+        <v>18.34</v>
       </c>
       <c r="F35" s="1">
-        <v>17.329999999999998</v>
+        <v>17.39</v>
       </c>
       <c r="G35" s="1">
-        <v>16.37</v>
+        <v>16.43</v>
       </c>
       <c r="H35" s="1">
-        <v>15.89</v>
+        <v>15.96</v>
       </c>
       <c r="I35" s="1">
+        <v>15.43</v>
+      </c>
+      <c r="J35" s="1">
+        <v>15.25</v>
+      </c>
+      <c r="K35" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="L35" s="1">
         <v>15.37</v>
-      </c>
-      <c r="J35" s="1">
-        <v>15.19</v>
-      </c>
-      <c r="K35" s="1">
-        <v>15.23</v>
-      </c>
-      <c r="L35" s="1">
-        <v>15.3</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2084,37 +2084,37 @@
         <v>46935</v>
       </c>
       <c r="B37" s="1">
-        <v>21.86</v>
+        <v>21.93</v>
       </c>
       <c r="C37" s="1">
-        <v>21.26</v>
+        <v>21.32</v>
       </c>
       <c r="D37" s="1">
-        <v>20.53</v>
+        <v>20.6</v>
       </c>
       <c r="E37" s="1">
-        <v>18.399999999999999</v>
+        <v>18.71</v>
       </c>
       <c r="F37" s="1">
-        <v>17.260000000000002</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="G37" s="1">
-        <v>16.46</v>
+        <v>16.53</v>
       </c>
       <c r="H37" s="1">
-        <v>15.98</v>
+        <v>16.05</v>
       </c>
       <c r="I37" s="1">
-        <v>15.46</v>
+        <v>15.53</v>
       </c>
       <c r="J37" s="1">
-        <v>15.29</v>
+        <v>15.36</v>
       </c>
       <c r="K37" s="1">
-        <v>15.33</v>
+        <v>15.4</v>
       </c>
       <c r="L37" s="1">
-        <v>15.4</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2122,37 +2122,37 @@
         <v>47119</v>
       </c>
       <c r="B38" s="1">
-        <v>22.64</v>
+        <v>22.68</v>
       </c>
       <c r="C38" s="1">
-        <v>21.98</v>
+        <v>22.02</v>
       </c>
       <c r="D38" s="1">
-        <v>21.22</v>
+        <v>21.26</v>
       </c>
       <c r="E38" s="1">
-        <v>19.350000000000001</v>
+        <v>19.39</v>
       </c>
       <c r="F38" s="1">
-        <v>17.920000000000002</v>
+        <v>17.97</v>
       </c>
       <c r="G38" s="1">
-        <v>17.079999999999998</v>
+        <v>17.13</v>
       </c>
       <c r="H38" s="1">
-        <v>16.57</v>
+        <v>16.62</v>
       </c>
       <c r="I38" s="1">
-        <v>16.02</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="J38" s="1">
-        <v>15.79</v>
+        <v>15.84</v>
       </c>
       <c r="K38" s="1">
-        <v>15.82</v>
+        <v>15.87</v>
       </c>
       <c r="L38" s="1">
-        <v>15.88</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2236,37 +2236,37 @@
         <v>10959</v>
       </c>
       <c r="B41" s="1">
-        <v>23.13</v>
+        <v>23.14</v>
       </c>
       <c r="C41" s="1">
-        <v>22.46</v>
+        <v>22.48</v>
       </c>
       <c r="D41" s="1">
-        <v>21.7</v>
+        <v>21.72</v>
       </c>
       <c r="E41" s="1">
-        <v>19.829999999999998</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="F41" s="1">
-        <v>18.41</v>
+        <v>18.43</v>
       </c>
       <c r="G41" s="1">
-        <v>17.559999999999999</v>
+        <v>17.579999999999998</v>
       </c>
       <c r="H41" s="1">
-        <v>17.04</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="I41" s="1">
-        <v>16.48</v>
+        <v>16.489999999999998</v>
       </c>
       <c r="J41" s="1">
-        <v>16.23</v>
+        <v>16.239999999999998</v>
       </c>
       <c r="K41" s="1">
-        <v>16.27</v>
+        <v>16.28</v>
       </c>
       <c r="L41" s="1">
-        <v>16.34</v>
+        <v>16.350000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2322,9 +2322,7 @@
       <c r="L43" s="1"/>
     </row>
     <row r="44" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="A44" s="2"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -2339,7 +2337,7 @@
     </row>
     <row r="45" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2355,7 +2353,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2371,7 +2369,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2386,9 +2384,7 @@
       <c r="L47" s="1"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="A48" s="2"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -2403,7 +2399,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2417,6 +2413,38 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
     </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/ddeprofit.xlsx
+++ b/ddeprofit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE06337-0B3E-4657-AC2A-9EFD0D1E8FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E55CC6C-8AB9-4B06-B47A-58C7D706FD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="superficie_de_volatilidade_de_dolar" localSheetId="1">base_b3!$A$1:$L$51</definedName>
+    <definedName name="superficie_de_volatilidade_de_dolar" localSheetId="1">base_b3!$A$1:$L$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -175,9 +175,6 @@
     <t>GLDFUT</t>
   </si>
   <si>
-    <t>Delta %</t>
-  </si>
-  <si>
     <t xml:space="preserve"> * A superfície de volatilidade de dólar é construída com base nas informações coletadas por um pool de Informantes às 18h</t>
   </si>
   <si>
@@ -187,7 +184,10 @@
     <t xml:space="preserve">                                                                                                                                                                                                               Download do arquivo</t>
   </si>
   <si>
-    <t xml:space="preserve">         Atualizado em: 16/03/2026</t>
+    <t xml:space="preserve">         Atualizado em: 17/03/2026</t>
+  </si>
+  <si>
+    <t>Delta%</t>
   </si>
 </sst>
 </file>
@@ -297,49 +297,49 @@
       <ddeItem name="DI1FUT.ABE" advise="1">
         <values>
           <value>
-            <val>13.73</val>
+            <val>13.55</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.FEC" advise="1">
         <values>
           <value>
-            <val>13.930000000000001</val>
+            <val>13.535000000000002</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.MAX" advise="1">
         <values>
           <value>
-            <val>13.734999999999999</val>
+            <val>13.8</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.MIN" advise="1">
         <values>
           <value>
-            <val>13.51</val>
+            <val>13.37</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.NEG" advise="1">
         <values>
           <value>
-            <val>74403</val>
+            <val>98045</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.ULT" advise="1">
         <values>
           <value>
-            <val>13.535</val>
+            <val>13.605</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DI1FUT.VAR" advise="1">
         <values>
           <value>
-            <val>-2.835606604450831</val>
+            <val>0.51717768747690229</val>
           </value>
         </values>
       </ddeItem>
@@ -353,56 +353,56 @@
       <ddeItem name="DI1FUT.VOL" advise="1">
         <values>
           <value>
-            <val>60485327161.019997</val>
+            <val>62117723915.089996</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.ABE" advise="1">
         <values>
           <value>
-            <val>99.858219000000005</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.FEC" advise="1">
         <values>
           <value>
-            <val>99.857467999999997</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MAX" advise="1">
         <values>
           <value>
-            <val>100.111442</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.MIN" advise="1">
         <values>
           <value>
-            <val>99.673192</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.NEG" advise="1">
         <values>
           <value>
-            <val>7390</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.ULT" advise="1">
         <values>
           <value>
-            <val>99.800200000000004</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="DOLINDEX.VAR" advise="1">
         <values>
           <value>
-            <val>-5.7349741733887072E-2</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
@@ -416,56 +416,56 @@
       <ddeItem name="DOLINDEX.VOL" advise="1">
         <values>
           <value>
-            <val>738213.01773199998</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.ABE" advise="1">
         <values>
           <value>
-            <val>20.6</val>
+            <val>18.600000000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.FEC" advise="1">
         <values>
           <value>
-            <val>22.5</val>
+            <val>20.3</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.MAX" advise="1">
         <values>
           <value>
-            <val>20.9</val>
+            <val>19.399999999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.MIN" advise="1">
         <values>
           <value>
-            <val>19.8</val>
+            <val>18.100000000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.NEG" advise="1">
         <values>
           <value>
-            <val>174</val>
+            <val>153</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.ULT" advise="1">
         <values>
           <value>
-            <val>20.3</val>
+            <val>19.399999999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="FRP0.VAR" advise="1">
         <values>
           <value>
-            <val>-9.7777777777777715</val>
+            <val>-4.4334975369458078</val>
           </value>
         </values>
       </ddeItem>
@@ -479,56 +479,56 @@
       <ddeItem name="FRP0.VOL" advise="1">
         <values>
           <value>
-            <val>7131245550</val>
+            <val>9509786375</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.ABE" advise="1">
         <values>
           <value>
-            <val>5032</val>
+            <val>5043</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.FEC" advise="1">
         <values>
           <value>
-            <val>5048.25</val>
+            <val>5043.75</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.MAX" advise="1">
         <values>
           <value>
-            <val>5069.25</val>
+            <val>5061.75</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.MIN" advise="1">
         <values>
           <value>
-            <val>5011.75</val>
+            <val>5006</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.NEG" advise="1">
         <values>
           <value>
-            <val>784</val>
+            <val>814</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.ULT" advise="1">
         <values>
           <value>
-            <val>5043.75</val>
+            <val>5035.75</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GLDFUT.VAR" advise="1">
         <values>
           <value>
-            <val>-8.9139800921117285E-2</val>
+            <val>-0.15861214374226051</val>
           </value>
         </values>
       </ddeItem>
@@ -542,7 +542,7 @@
       <ddeItem name="GLDFUT.VOL" advise="1">
         <values>
           <value>
-            <val>48905578.57</val>
+            <val>82612960.239999995</val>
           </value>
         </values>
       </ddeItem>
@@ -550,49 +550,49 @@
       <ddeItem name="USD/BRL.ABE" advise="1">
         <values>
           <value>
-            <val>5.2314999999999996</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.FEC" advise="1">
         <values>
           <value>
-            <val>5.2332999999999998</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MAX" advise="1">
         <values>
           <value>
-            <val>5.2504340000000003</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.MIN" advise="1">
         <values>
           <value>
-            <val>5.2304909999999998</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.NEG" advise="1">
         <values>
           <value>
-            <val>915</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.ULT" advise="1">
         <values>
           <value>
-            <val>5.2481999999999998</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USD/BRL.VAR" advise="1">
         <values>
           <value>
-            <val>0.28471518926870942</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
@@ -606,49 +606,49 @@
       <ddeItem name="USD/BRL.VOL" advise="1">
         <values>
           <value>
-            <val>4790.514013</val>
+            <val>0</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.ABE" advise="1">
         <values>
           <value>
-            <val>5304.5</val>
+            <val>5253</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.MAX" advise="1">
         <values>
           <value>
-            <val>5306.5</val>
+            <val>5261</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.MIN" advise="1">
         <values>
           <value>
-            <val>5246</val>
+            <val>5195.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.NEG" advise="1">
         <values>
           <value>
-            <val>707229</val>
+            <val>729445</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.ULT" advise="1">
         <values>
           <value>
-            <val>5252.5</val>
+            <val>5214.5</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="WDOFUT.VAR" advise="1">
         <values>
           <value>
-            <val>-1.8957788569293967</val>
+            <val>-0.72346501665873575</val>
           </value>
         </values>
       </ddeItem>
@@ -662,7 +662,7 @@
       <ddeItem name="WDOFUT.VOL" advise="1">
         <values>
           <value>
-            <val>142113673710</val>
+            <val>155147286945</val>
           </value>
         </values>
       </ddeItem>
@@ -1019,35 +1019,35 @@
       </c>
       <c r="K2" cm="1">
         <f t="array" ref="K2">[1]!DI1FUT.ULT</f>
-        <v>13.535</v>
+        <v>13.605</v>
       </c>
       <c r="L2" cm="1">
         <f t="array" ref="L2">[1]!DI1FUT.ABE</f>
-        <v>13.73</v>
+        <v>13.55</v>
       </c>
       <c r="M2" cm="1">
         <f t="array" ref="M2">[1]!DI1FUT.MAX</f>
-        <v>13.734999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="N2" cm="1">
         <f t="array" ref="N2">[1]!DI1FUT.MIN</f>
-        <v>13.51</v>
+        <v>13.37</v>
       </c>
       <c r="O2" cm="1">
         <f t="array" ref="O2">[1]!DI1FUT.FEC</f>
-        <v>13.930000000000001</v>
+        <v>13.535000000000002</v>
       </c>
       <c r="P2" cm="1">
         <f t="array" ref="P2">[1]!DI1FUT.VAR</f>
-        <v>-2.835606604450831</v>
+        <v>0.51717768747690229</v>
       </c>
       <c r="Q2" cm="1">
         <f t="array" ref="Q2">[1]!DI1FUT.NEG</f>
-        <v>74403</v>
+        <v>98045</v>
       </c>
       <c r="R2" cm="1">
         <f t="array" ref="R2">[1]!DI1FUT.VOL</f>
-        <v>60485327161.019997</v>
+        <v>62117723915.089996</v>
       </c>
       <c r="S2" t="str" cm="1">
         <f t="array" ref="S2">[1]!DI1FUT.VEN</f>
@@ -1060,35 +1060,35 @@
       </c>
       <c r="K3" cm="1">
         <f t="array" ref="K3">[1]!FRP0.ULT</f>
-        <v>20.3</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="L3" cm="1">
         <f t="array" ref="L3">[1]!FRP0.ABE</f>
-        <v>20.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="M3" cm="1">
         <f t="array" ref="M3">[1]!FRP0.MAX</f>
-        <v>20.9</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="N3" cm="1">
         <f t="array" ref="N3">[1]!FRP0.MIN</f>
-        <v>19.8</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="O3" cm="1">
         <f t="array" ref="O3">[1]!FRP0.FEC</f>
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="P3" cm="1">
         <f t="array" ref="P3">[1]!FRP0.VAR</f>
-        <v>-9.7777777777777715</v>
+        <v>-4.4334975369458078</v>
       </c>
       <c r="Q3" cm="1">
         <f t="array" ref="Q3">[1]!FRP0.NEG</f>
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="R3" cm="1">
         <f t="array" ref="R3">[1]!FRP0.VOL</f>
-        <v>7131245550</v>
+        <v>9509786375</v>
       </c>
       <c r="S3" t="str" cm="1">
         <f t="array" ref="S3">[1]!FRP0.VEN</f>
@@ -1101,35 +1101,35 @@
       </c>
       <c r="K4" cm="1">
         <f t="array" ref="K4">[1]!'USD/BRL.ULT'</f>
-        <v>5.2481999999999998</v>
+        <v>0</v>
       </c>
       <c r="L4" cm="1">
         <f t="array" ref="L4">[1]!'USD/BRL.ABE'</f>
-        <v>5.2314999999999996</v>
+        <v>0</v>
       </c>
       <c r="M4" cm="1">
         <f t="array" ref="M4">[1]!'USD/BRL.MAX'</f>
-        <v>5.2504340000000003</v>
+        <v>0</v>
       </c>
       <c r="N4" cm="1">
         <f t="array" ref="N4">[1]!'USD/BRL.MIN'</f>
-        <v>5.2304909999999998</v>
+        <v>0</v>
       </c>
       <c r="O4" cm="1">
         <f t="array" ref="O4">[1]!'USD/BRL.FEC'</f>
-        <v>5.2332999999999998</v>
+        <v>0</v>
       </c>
       <c r="P4" cm="1">
         <f t="array" ref="P4">[1]!'USD/BRL.VAR'</f>
-        <v>0.28471518926870942</v>
+        <v>0</v>
       </c>
       <c r="Q4" cm="1">
         <f t="array" ref="Q4">[1]!'USD/BRL.NEG'</f>
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="R4" cm="1">
         <f t="array" ref="R4">[1]!'USD/BRL.VOL'</f>
-        <v>4790.514013</v>
+        <v>0</v>
       </c>
       <c r="S4" t="str" cm="1">
         <f t="array" ref="S4">[1]!'USD/BRL.VEN'</f>
@@ -1142,34 +1142,34 @@
       </c>
       <c r="K5" cm="1">
         <f t="array" ref="K5">[1]!WDOFUT.ULT</f>
-        <v>5252.5</v>
+        <v>5214.5</v>
       </c>
       <c r="L5" cm="1">
         <f t="array" ref="L5">[1]!WDOFUT.ABE</f>
-        <v>5304.5</v>
+        <v>5253</v>
       </c>
       <c r="M5" cm="1">
         <f t="array" ref="M5">[1]!WDOFUT.MAX</f>
-        <v>5306.5</v>
+        <v>5261</v>
       </c>
       <c r="N5" cm="1">
         <f t="array" ref="N5">[1]!WDOFUT.MIN</f>
-        <v>5246</v>
+        <v>5195.5</v>
       </c>
       <c r="O5">
-        <v>5339.5</v>
+        <v>5314.5</v>
       </c>
       <c r="P5" cm="1">
         <f t="array" ref="P5">[1]!WDOFUT.VAR</f>
-        <v>-1.8957788569293967</v>
+        <v>-0.72346501665873575</v>
       </c>
       <c r="Q5" cm="1">
         <f t="array" ref="Q5">[1]!WDOFUT.NEG</f>
-        <v>707229</v>
+        <v>729445</v>
       </c>
       <c r="R5" cm="1">
         <f t="array" ref="R5">[1]!WDOFUT.VOL</f>
-        <v>142113673710</v>
+        <v>155147286945</v>
       </c>
       <c r="S5" t="str" cm="1">
         <f t="array" ref="S5">[1]!WDOFUT.VEN</f>
@@ -1182,35 +1182,35 @@
       </c>
       <c r="K6" cm="1">
         <f t="array" ref="K6">[1]!DOLINDEX.ULT</f>
-        <v>99.800200000000004</v>
+        <v>0</v>
       </c>
       <c r="L6" cm="1">
         <f t="array" ref="L6">[1]!DOLINDEX.ABE</f>
-        <v>99.858219000000005</v>
+        <v>0</v>
       </c>
       <c r="M6" cm="1">
         <f t="array" ref="M6">[1]!DOLINDEX.MAX</f>
-        <v>100.111442</v>
+        <v>0</v>
       </c>
       <c r="N6" cm="1">
         <f t="array" ref="N6">[1]!DOLINDEX.MIN</f>
-        <v>99.673192</v>
+        <v>0</v>
       </c>
       <c r="O6" cm="1">
         <f t="array" ref="O6">[1]!DOLINDEX.FEC</f>
-        <v>99.857467999999997</v>
+        <v>0</v>
       </c>
       <c r="P6" cm="1">
         <f t="array" ref="P6">[1]!DOLINDEX.VAR</f>
-        <v>-5.7349741733887072E-2</v>
+        <v>0</v>
       </c>
       <c r="Q6" cm="1">
         <f t="array" ref="Q6">[1]!DOLINDEX.NEG</f>
-        <v>7390</v>
+        <v>0</v>
       </c>
       <c r="R6" cm="1">
         <f t="array" ref="R6">[1]!DOLINDEX.VOL</f>
-        <v>738213.01773199998</v>
+        <v>0</v>
       </c>
       <c r="S6" t="str" cm="1">
         <f t="array" ref="S6">[1]!DOLINDEX.VEN</f>
@@ -1223,35 +1223,35 @@
       </c>
       <c r="K7" cm="1">
         <f t="array" ref="K7">[1]!GLDFUT.ULT</f>
-        <v>5043.75</v>
+        <v>5035.75</v>
       </c>
       <c r="L7" cm="1">
         <f t="array" ref="L7">[1]!GLDFUT.ABE</f>
-        <v>5032</v>
+        <v>5043</v>
       </c>
       <c r="M7" cm="1">
         <f t="array" ref="M7">[1]!GLDFUT.MAX</f>
-        <v>5069.25</v>
+        <v>5061.75</v>
       </c>
       <c r="N7" cm="1">
         <f t="array" ref="N7">[1]!GLDFUT.MIN</f>
-        <v>5011.75</v>
+        <v>5006</v>
       </c>
       <c r="O7" cm="1">
         <f t="array" ref="O7">[1]!GLDFUT.FEC</f>
-        <v>5048.25</v>
+        <v>5043.75</v>
       </c>
       <c r="P7" cm="1">
         <f t="array" ref="P7">[1]!GLDFUT.VAR</f>
-        <v>-8.9139800921117285E-2</v>
+        <v>-0.15861214374226051</v>
       </c>
       <c r="Q7" cm="1">
         <f t="array" ref="Q7">[1]!GLDFUT.NEG</f>
-        <v>784</v>
+        <v>814</v>
       </c>
       <c r="R7" cm="1">
         <f t="array" ref="R7">[1]!GLDFUT.VOL</f>
-        <v>48905578.57</v>
+        <v>82612960.239999995</v>
       </c>
       <c r="S7" t="str" cm="1">
         <f t="array" ref="S7">[1]!GLDFUT.VEN</f>
@@ -1266,10 +1266,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Planilha10"/>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11" style="5" customWidth="1"/>
     <col min="2" max="12" width="9.140625" style="5" customWidth="1"/>
     <col min="13" max="16384" width="10.28515625" style="5"/>
   </cols>
@@ -1354,12 +1354,12 @@
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B18" s="4">
         <v>1</v>
@@ -1400,37 +1400,37 @@
         <v>46113</v>
       </c>
       <c r="B19" s="4">
-        <v>21.99</v>
+        <v>21.26</v>
       </c>
       <c r="C19" s="4">
-        <v>20.97</v>
+        <v>20.23</v>
       </c>
       <c r="D19" s="4">
-        <v>19.84</v>
+        <v>19.11</v>
       </c>
       <c r="E19" s="4">
-        <v>17.34</v>
+        <v>16.61</v>
       </c>
       <c r="F19" s="4">
-        <v>16.059999999999999</v>
+        <v>15.3</v>
       </c>
       <c r="G19" s="4">
-        <v>15.09</v>
+        <v>14.36</v>
       </c>
       <c r="H19" s="4">
-        <v>14.34</v>
+        <v>13.6</v>
       </c>
       <c r="I19" s="4">
-        <v>13.59</v>
+        <v>12.84</v>
       </c>
       <c r="J19" s="4">
-        <v>12.98</v>
+        <v>12.24</v>
       </c>
       <c r="K19" s="4">
-        <v>14.01</v>
+        <v>13.54</v>
       </c>
       <c r="L19" s="4">
-        <v>15.7</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1438,37 +1438,37 @@
         <v>46143</v>
       </c>
       <c r="B20" s="4">
-        <v>21.46</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4">
-        <v>20.71</v>
+        <v>20.25</v>
       </c>
       <c r="D20" s="4">
-        <v>19.79</v>
+        <v>19.329999999999998</v>
       </c>
       <c r="E20" s="4">
-        <v>17.13</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="F20" s="4">
-        <v>15.75</v>
+        <v>15.29</v>
       </c>
       <c r="G20" s="4">
-        <v>14.73</v>
+        <v>14.26</v>
       </c>
       <c r="H20" s="4">
-        <v>13.96</v>
+        <v>13.49</v>
       </c>
       <c r="I20" s="4">
-        <v>13.14</v>
+        <v>12.67</v>
       </c>
       <c r="J20" s="4">
-        <v>12.51</v>
+        <v>12.04</v>
       </c>
       <c r="K20" s="4">
-        <v>12.5</v>
+        <v>12.02</v>
       </c>
       <c r="L20" s="4">
-        <v>12.5</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1476,37 +1476,37 @@
         <v>46174</v>
       </c>
       <c r="B21" s="4">
-        <v>21.4</v>
+        <v>20.91</v>
       </c>
       <c r="C21" s="4">
-        <v>20.47</v>
+        <v>20</v>
       </c>
       <c r="D21" s="4">
-        <v>19.420000000000002</v>
+        <v>18.97</v>
       </c>
       <c r="E21" s="4">
-        <v>16.95</v>
+        <v>16.47</v>
       </c>
       <c r="F21" s="4">
-        <v>15.9</v>
+        <v>15.43</v>
       </c>
       <c r="G21" s="4">
-        <v>14.73</v>
+        <v>14.23</v>
       </c>
       <c r="H21" s="4">
-        <v>14.04</v>
+        <v>13.53</v>
       </c>
       <c r="I21" s="4">
-        <v>13.3</v>
+        <v>12.78</v>
       </c>
       <c r="J21" s="4">
-        <v>12.77</v>
+        <v>12.23</v>
       </c>
       <c r="K21" s="4">
-        <v>12.79</v>
+        <v>12.21</v>
       </c>
       <c r="L21" s="4">
-        <v>12.83</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1514,37 +1514,37 @@
         <v>46204</v>
       </c>
       <c r="B22" s="4">
-        <v>21.47</v>
+        <v>21.09</v>
       </c>
       <c r="C22" s="4">
-        <v>20.52</v>
+        <v>20.14</v>
       </c>
       <c r="D22" s="4">
-        <v>19.440000000000001</v>
+        <v>19.059999999999999</v>
       </c>
       <c r="E22" s="4">
-        <v>16.940000000000001</v>
+        <v>16.53</v>
       </c>
       <c r="F22" s="4">
-        <v>15.88</v>
+        <v>15.47</v>
       </c>
       <c r="G22" s="4">
-        <v>14.72</v>
+        <v>14.28</v>
       </c>
       <c r="H22" s="4">
-        <v>14.06</v>
+        <v>13.6</v>
       </c>
       <c r="I22" s="4">
-        <v>13.36</v>
+        <v>12.88</v>
       </c>
       <c r="J22" s="4">
-        <v>12.91</v>
+        <v>12.41</v>
       </c>
       <c r="K22" s="4">
-        <v>12.97</v>
+        <v>12.43</v>
       </c>
       <c r="L22" s="4">
-        <v>13.05</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1552,37 +1552,37 @@
         <v>46235</v>
       </c>
       <c r="B23" s="4">
-        <v>21.16</v>
+        <v>21</v>
       </c>
       <c r="C23" s="4">
-        <v>20.25</v>
+        <v>20.079999999999998</v>
       </c>
       <c r="D23" s="4">
-        <v>19.239999999999998</v>
+        <v>19.04</v>
       </c>
       <c r="E23" s="4">
-        <v>16.850000000000001</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="F23" s="4">
-        <v>15.81</v>
+        <v>15.56</v>
       </c>
       <c r="G23" s="4">
-        <v>14.69</v>
+        <v>14.4</v>
       </c>
       <c r="H23" s="4">
-        <v>14.05</v>
+        <v>13.75</v>
       </c>
       <c r="I23" s="4">
-        <v>13.39</v>
+        <v>13.06</v>
       </c>
       <c r="J23" s="4">
-        <v>13.01</v>
+        <v>12.64</v>
       </c>
       <c r="K23" s="4">
-        <v>13.05</v>
+        <v>12.65</v>
       </c>
       <c r="L23" s="4">
-        <v>13.11</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1590,37 +1590,37 @@
         <v>46266</v>
       </c>
       <c r="B24" s="4">
-        <v>20.96</v>
+        <v>21</v>
       </c>
       <c r="C24" s="4">
         <v>20.12</v>
       </c>
       <c r="D24" s="4">
-        <v>19.16</v>
+        <v>19.12</v>
       </c>
       <c r="E24" s="4">
-        <v>16.86</v>
+        <v>16.78</v>
       </c>
       <c r="F24" s="4">
-        <v>15.84</v>
+        <v>15.74</v>
       </c>
       <c r="G24" s="4">
-        <v>14.75</v>
+        <v>14.61</v>
       </c>
       <c r="H24" s="4">
-        <v>14.15</v>
+        <v>13.99</v>
       </c>
       <c r="I24" s="4">
-        <v>13.52</v>
+        <v>13.33</v>
       </c>
       <c r="J24" s="4">
-        <v>13.21</v>
+        <v>12.97</v>
       </c>
       <c r="K24" s="4">
-        <v>13.24</v>
+        <v>12.99</v>
       </c>
       <c r="L24" s="4">
-        <v>13.29</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1628,37 +1628,37 @@
         <v>46296</v>
       </c>
       <c r="B25" s="4">
-        <v>21.08</v>
+        <v>21.34</v>
       </c>
       <c r="C25" s="4">
-        <v>20.329999999999998</v>
+        <v>20.53</v>
       </c>
       <c r="D25" s="4">
-        <v>19.45</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="E25" s="4">
-        <v>17.100000000000001</v>
+        <v>17.18</v>
       </c>
       <c r="F25" s="4">
-        <v>16.059999999999999</v>
+        <v>16.12</v>
       </c>
       <c r="G25" s="4">
-        <v>14.96</v>
+        <v>14.89</v>
       </c>
       <c r="H25" s="4">
-        <v>14.35</v>
+        <v>14.36</v>
       </c>
       <c r="I25" s="4">
-        <v>13.74</v>
+        <v>13.71</v>
       </c>
       <c r="J25" s="4">
-        <v>13.48</v>
+        <v>13.41</v>
       </c>
       <c r="K25" s="4">
-        <v>13.5</v>
+        <v>13.43</v>
       </c>
       <c r="L25" s="4">
-        <v>13.52</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1666,37 +1666,37 @@
         <v>46327</v>
       </c>
       <c r="B26" s="4">
-        <v>21.34</v>
+        <v>21.84</v>
       </c>
       <c r="C26" s="4">
-        <v>20.65</v>
+        <v>21.14</v>
       </c>
       <c r="D26" s="4">
-        <v>19.809999999999999</v>
+        <v>20.28</v>
       </c>
       <c r="E26" s="4">
-        <v>17.399999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="F26" s="4">
-        <v>16.149999999999999</v>
+        <v>16.71</v>
       </c>
       <c r="G26" s="4">
-        <v>15.25</v>
+        <v>15.58</v>
       </c>
       <c r="H26" s="4">
-        <v>14.66</v>
+        <v>14.96</v>
       </c>
       <c r="I26" s="4">
-        <v>14.02</v>
+        <v>14.27</v>
       </c>
       <c r="J26" s="4">
-        <v>13.76</v>
+        <v>13.94</v>
       </c>
       <c r="K26" s="4">
-        <v>13.79</v>
+        <v>13.97</v>
       </c>
       <c r="L26" s="4">
-        <v>13.86</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1704,37 +1704,37 @@
         <v>46357</v>
       </c>
       <c r="B27" s="4">
-        <v>21.28</v>
+        <v>21.85</v>
       </c>
       <c r="C27" s="4">
-        <v>20.64</v>
+        <v>21.11</v>
       </c>
       <c r="D27" s="4">
-        <v>19.89</v>
+        <v>20.28</v>
       </c>
       <c r="E27" s="4">
-        <v>17.89</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="F27" s="4">
-        <v>16.37</v>
+        <v>16.66</v>
       </c>
       <c r="G27" s="4">
-        <v>15.5</v>
+        <v>15.77</v>
       </c>
       <c r="H27" s="4">
-        <v>14.66</v>
+        <v>15.17</v>
       </c>
       <c r="I27" s="4">
-        <v>14.19</v>
+        <v>14.58</v>
       </c>
       <c r="J27" s="4">
-        <v>14.17</v>
+        <v>14.35</v>
       </c>
       <c r="K27" s="4">
-        <v>14.11</v>
+        <v>14.34</v>
       </c>
       <c r="L27" s="4">
-        <v>14.03</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1742,37 +1742,37 @@
         <v>46388</v>
       </c>
       <c r="B28" s="4">
-        <v>21.22</v>
+        <v>21.78</v>
       </c>
       <c r="C28" s="4">
-        <v>20.58</v>
+        <v>21.04</v>
       </c>
       <c r="D28" s="4">
-        <v>19.8</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="E28" s="4">
-        <v>17.579999999999998</v>
+        <v>17.91</v>
       </c>
       <c r="F28" s="4">
-        <v>16.64</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="G28" s="4">
-        <v>15.6</v>
+        <v>15.89</v>
       </c>
       <c r="H28" s="4">
-        <v>15.05</v>
+        <v>15.33</v>
       </c>
       <c r="I28" s="4">
-        <v>14.53</v>
+        <v>14.79</v>
       </c>
       <c r="J28" s="4">
-        <v>14.38</v>
+        <v>14.6</v>
       </c>
       <c r="K28" s="4">
-        <v>14.31</v>
+        <v>14.59</v>
       </c>
       <c r="L28" s="4">
-        <v>14.24</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1780,37 +1780,37 @@
         <v>46419</v>
       </c>
       <c r="B29" s="4">
-        <v>21.33</v>
+        <v>21.93</v>
       </c>
       <c r="C29" s="4">
-        <v>20.64</v>
+        <v>21.25</v>
       </c>
       <c r="D29" s="4">
-        <v>19.850000000000001</v>
+        <v>20.43</v>
       </c>
       <c r="E29" s="4">
-        <v>17.84</v>
+        <v>18.079999999999998</v>
       </c>
       <c r="F29" s="4">
-        <v>16.34</v>
+        <v>17.05</v>
       </c>
       <c r="G29" s="4">
-        <v>15.48</v>
+        <v>15.98</v>
       </c>
       <c r="H29" s="4">
-        <v>14.92</v>
+        <v>15.4</v>
       </c>
       <c r="I29" s="4">
-        <v>14.32</v>
+        <v>14.78</v>
       </c>
       <c r="J29" s="4">
-        <v>14.1</v>
+        <v>14.51</v>
       </c>
       <c r="K29" s="4">
-        <v>14.14</v>
+        <v>14.55</v>
       </c>
       <c r="L29" s="4">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1818,37 +1818,37 @@
         <v>46447</v>
       </c>
       <c r="B30" s="4">
-        <v>21.3</v>
+        <v>21.87</v>
       </c>
       <c r="C30" s="4">
-        <v>20.62</v>
+        <v>21.21</v>
       </c>
       <c r="D30" s="4">
-        <v>19.84</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E30" s="4">
-        <v>17.88</v>
+        <v>18.12</v>
       </c>
       <c r="F30" s="4">
-        <v>16.420000000000002</v>
+        <v>17.11</v>
       </c>
       <c r="G30" s="4">
-        <v>15.57</v>
+        <v>16.07</v>
       </c>
       <c r="H30" s="4">
-        <v>15.04</v>
+        <v>15.52</v>
       </c>
       <c r="I30" s="4">
-        <v>14.45</v>
+        <v>14.92</v>
       </c>
       <c r="J30" s="4">
-        <v>14.25</v>
+        <v>14.69</v>
       </c>
       <c r="K30" s="4">
-        <v>14.29</v>
+        <v>14.72</v>
       </c>
       <c r="L30" s="4">
-        <v>14.36</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1856,37 +1856,37 @@
         <v>46478</v>
       </c>
       <c r="B31" s="4">
-        <v>20.73</v>
+        <v>21.61</v>
       </c>
       <c r="C31" s="4">
-        <v>20.18</v>
+        <v>20.85</v>
       </c>
       <c r="D31" s="4">
-        <v>19.510000000000002</v>
+        <v>19.97</v>
       </c>
       <c r="E31" s="4">
-        <v>17.62</v>
+        <v>17.77</v>
       </c>
       <c r="F31" s="4">
-        <v>16.29</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="G31" s="4">
-        <v>15.46</v>
+        <v>15.92</v>
       </c>
       <c r="H31" s="4">
+        <v>15.43</v>
+      </c>
+      <c r="I31" s="4">
         <v>14.97</v>
       </c>
-      <c r="I31" s="4">
-        <v>14.52</v>
-      </c>
       <c r="J31" s="4">
-        <v>14.54</v>
+        <v>14.99</v>
       </c>
       <c r="K31" s="4">
-        <v>14.48</v>
+        <v>15.09</v>
       </c>
       <c r="L31" s="4">
-        <v>14.37</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1894,37 +1894,37 @@
         <v>46569</v>
       </c>
       <c r="B32" s="4">
-        <v>21.3</v>
+        <v>21.48</v>
       </c>
       <c r="C32" s="4">
-        <v>20.64</v>
+        <v>20.78</v>
       </c>
       <c r="D32" s="4">
-        <v>19.89</v>
+        <v>20</v>
       </c>
       <c r="E32" s="4">
-        <v>18.100000000000001</v>
+        <v>18.21</v>
       </c>
       <c r="F32" s="4">
-        <v>16.73</v>
+        <v>16.84</v>
       </c>
       <c r="G32" s="4">
-        <v>15.97</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="H32" s="4">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="I32" s="4">
-        <v>15.05</v>
+        <v>15.14</v>
       </c>
       <c r="J32" s="4">
-        <v>14.99</v>
+        <v>15.08</v>
       </c>
       <c r="K32" s="4">
-        <v>15.01</v>
+        <v>15.12</v>
       </c>
       <c r="L32" s="4">
-        <v>15.04</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1962,7 +1962,7 @@
         <v>15.53</v>
       </c>
       <c r="L33" s="4">
-        <v>15.78</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2008,37 +2008,37 @@
         <v>46753</v>
       </c>
       <c r="B35" s="1">
-        <v>21.78</v>
+        <v>21.68</v>
       </c>
       <c r="C35" s="1">
-        <v>21.16</v>
+        <v>21.06</v>
       </c>
       <c r="D35" s="1">
-        <v>20.41</v>
+        <v>20.329999999999998</v>
       </c>
       <c r="E35" s="1">
-        <v>18.34</v>
+        <v>18.29</v>
       </c>
       <c r="F35" s="1">
-        <v>17.39</v>
+        <v>17.36</v>
       </c>
       <c r="G35" s="1">
-        <v>16.43</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="H35" s="1">
-        <v>15.96</v>
+        <v>15.97</v>
       </c>
       <c r="I35" s="1">
-        <v>15.43</v>
+        <v>15.47</v>
       </c>
       <c r="J35" s="1">
-        <v>15.25</v>
+        <v>15.33</v>
       </c>
       <c r="K35" s="1">
-        <v>15.3</v>
+        <v>15.38</v>
       </c>
       <c r="L35" s="1">
-        <v>15.37</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2084,37 +2084,37 @@
         <v>46935</v>
       </c>
       <c r="B37" s="1">
-        <v>21.93</v>
+        <v>21.77</v>
       </c>
       <c r="C37" s="1">
-        <v>21.32</v>
+        <v>21.13</v>
       </c>
       <c r="D37" s="1">
-        <v>20.6</v>
+        <v>20.41</v>
       </c>
       <c r="E37" s="1">
-        <v>18.71</v>
+        <v>18.62</v>
       </c>
       <c r="F37" s="1">
-        <v>17.329999999999998</v>
+        <v>17.29</v>
       </c>
       <c r="G37" s="1">
-        <v>16.53</v>
+        <v>16.52</v>
       </c>
       <c r="H37" s="1">
-        <v>16.05</v>
+        <v>16.07</v>
       </c>
       <c r="I37" s="1">
+        <v>15.58</v>
+      </c>
+      <c r="J37" s="1">
+        <v>15.47</v>
+      </c>
+      <c r="K37" s="1">
         <v>15.53</v>
       </c>
-      <c r="J37" s="1">
-        <v>15.36</v>
-      </c>
-      <c r="K37" s="1">
-        <v>15.4</v>
-      </c>
       <c r="L37" s="1">
-        <v>15.47</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2122,37 +2122,37 @@
         <v>47119</v>
       </c>
       <c r="B38" s="1">
-        <v>22.68</v>
+        <v>22.52</v>
       </c>
       <c r="C38" s="1">
-        <v>22.02</v>
+        <v>21.87</v>
       </c>
       <c r="D38" s="1">
-        <v>21.26</v>
+        <v>21.13</v>
       </c>
       <c r="E38" s="1">
-        <v>19.39</v>
+        <v>19.3</v>
       </c>
       <c r="F38" s="1">
-        <v>17.97</v>
+        <v>17.93</v>
       </c>
       <c r="G38" s="1">
-        <v>17.13</v>
+        <v>17.12</v>
       </c>
       <c r="H38" s="1">
-        <v>16.62</v>
+        <v>16.63</v>
       </c>
       <c r="I38" s="1">
-        <v>16.059999999999999</v>
+        <v>16.12</v>
       </c>
       <c r="J38" s="1">
-        <v>15.84</v>
+        <v>15.95</v>
       </c>
       <c r="K38" s="1">
-        <v>15.87</v>
+        <v>16</v>
       </c>
       <c r="L38" s="1">
-        <v>15.92</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2236,37 +2236,37 @@
         <v>10959</v>
       </c>
       <c r="B41" s="1">
-        <v>23.14</v>
+        <v>22.98</v>
       </c>
       <c r="C41" s="1">
-        <v>22.48</v>
+        <v>22.33</v>
       </c>
       <c r="D41" s="1">
-        <v>21.72</v>
+        <v>21.58</v>
       </c>
       <c r="E41" s="1">
-        <v>19.850000000000001</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="F41" s="1">
-        <v>18.43</v>
+        <v>18.39</v>
       </c>
       <c r="G41" s="1">
-        <v>17.579999999999998</v>
+        <v>17.57</v>
       </c>
       <c r="H41" s="1">
-        <v>17.059999999999999</v>
+        <v>17.07</v>
       </c>
       <c r="I41" s="1">
-        <v>16.489999999999998</v>
+        <v>16.55</v>
       </c>
       <c r="J41" s="1">
-        <v>16.239999999999998</v>
+        <v>16.39</v>
       </c>
       <c r="K41" s="1">
-        <v>16.28</v>
+        <v>16.43</v>
       </c>
       <c r="L41" s="1">
-        <v>16.350000000000001</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2274,41 +2274,43 @@
         <v>11324</v>
       </c>
       <c r="B42" s="1">
-        <v>23.21</v>
+        <v>23.04</v>
       </c>
       <c r="C42" s="1">
-        <v>22.58</v>
+        <v>22.43</v>
       </c>
       <c r="D42" s="1">
-        <v>21.85</v>
+        <v>21.71</v>
       </c>
       <c r="E42" s="1">
-        <v>19.91</v>
+        <v>19.82</v>
       </c>
       <c r="F42" s="1">
-        <v>18.489999999999998</v>
+        <v>18.45</v>
       </c>
       <c r="G42" s="1">
-        <v>17.63</v>
+        <v>17.62</v>
       </c>
       <c r="H42" s="1">
-        <v>16.850000000000001</v>
+        <v>16.88</v>
       </c>
       <c r="I42" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="J42" s="1">
         <v>16.43</v>
       </c>
-      <c r="J42" s="1">
-        <v>16.32</v>
-      </c>
       <c r="K42" s="1">
-        <v>16.350000000000001</v>
+        <v>16.47</v>
       </c>
       <c r="L42" s="1">
-        <v>16.39</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="2"/>
+      <c r="A43" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -2322,7 +2324,9 @@
       <c r="L43" s="1"/>
     </row>
     <row r="44" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2"/>
+      <c r="A44" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -2337,7 +2341,7 @@
     </row>
     <row r="45" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2352,9 +2356,7 @@
       <c r="L45" s="1"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="A46" s="2"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -2369,7 +2371,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2384,7 +2386,9 @@
       <c r="L47" s="1"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -2399,7 +2403,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2413,38 +2417,6 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/ddeprofit.xlsx
+++ b/ddeprofit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E55CC6C-8AB9-4B06-B47A-58C7D706FD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212009A8-E6E0-4887-8601-3AD5ED3722ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1157,7 +1157,7 @@
         <v>5195.5</v>
       </c>
       <c r="O5">
-        <v>5314.5</v>
+        <v>5214.5</v>
       </c>
       <c r="P5" cm="1">
         <f t="array" ref="P5">[1]!WDOFUT.VAR</f>
